--- a/templates/master_template_12.xlsx
+++ b/templates/master_template_12.xlsx
@@ -772,7 +772,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O91"/>
+  <dimension ref="A1:O92"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="6" customWidth="1" style="27" min="1" max="1"/>
@@ -954,62 +954,38 @@
       <c r="N6" s="42" t="n"/>
       <c r="O6" s="42" t="n"/>
     </row>
-    <row r="7" ht="15" customHeight="1" s="28">
-      <c r="A7" s="43" t="inlineStr">
+    <row r="7" ht="12" customHeight="1" s="28">
+      <c r="A7" s="41" t="inlineStr">
+        <is>
+          <t>보장기간</t>
+        </is>
+      </c>
+      <c r="C7" s="42" t="n"/>
+      <c r="D7" s="42" t="n"/>
+      <c r="E7" s="42" t="n"/>
+      <c r="F7" s="42" t="n"/>
+      <c r="G7" s="42" t="n"/>
+      <c r="H7" s="42" t="n"/>
+      <c r="I7" s="42" t="n"/>
+      <c r="J7" s="42" t="n"/>
+      <c r="K7" s="42" t="n"/>
+      <c r="L7" s="42" t="n"/>
+      <c r="M7" s="42" t="n"/>
+      <c r="N7" s="42" t="n"/>
+      <c r="O7" s="42" t="n"/>
+    </row>
+    <row r="8" ht="12.75" customHeight="1" s="28">
+      <c r="A8" s="43" t="inlineStr">
         <is>
           <t>▶  월 납입 보험료</t>
         </is>
       </c>
-      <c r="C7" s="44" t="n"/>
-      <c r="D7" s="44" t="n"/>
-      <c r="E7" s="44" t="n"/>
-      <c r="F7" s="44" t="n"/>
-      <c r="G7" s="44" t="n"/>
-      <c r="H7" s="44" t="n"/>
-      <c r="I7" s="44" t="n"/>
-      <c r="J7" s="44" t="n"/>
-      <c r="K7" s="44" t="n"/>
-      <c r="L7" s="44" t="n"/>
-      <c r="M7" s="44" t="n"/>
-      <c r="N7" s="44" t="n"/>
-      <c r="O7" s="44">
-        <f>SUM(C7:N7)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="12.75" customHeight="1" s="28">
-      <c r="A8" s="45" t="inlineStr">
+    </row>
+    <row r="9" ht="10.5" customHeight="1" s="28">
+      <c r="A9" s="45" t="inlineStr">
         <is>
           <t>▶  사망 보장</t>
         </is>
-      </c>
-    </row>
-    <row r="9" ht="10.5" customHeight="1" s="28">
-      <c r="A9" s="46" t="inlineStr">
-        <is>
-          <t>사망</t>
-        </is>
-      </c>
-      <c r="B9" s="47" t="inlineStr">
-        <is>
-          <t>일반사망</t>
-        </is>
-      </c>
-      <c r="C9" s="48" t="n"/>
-      <c r="D9" s="48" t="n"/>
-      <c r="E9" s="48" t="n"/>
-      <c r="F9" s="48" t="n"/>
-      <c r="G9" s="48" t="n"/>
-      <c r="H9" s="48" t="n"/>
-      <c r="I9" s="48" t="n"/>
-      <c r="J9" s="48" t="n"/>
-      <c r="K9" s="48" t="n"/>
-      <c r="L9" s="48" t="n"/>
-      <c r="M9" s="48" t="n"/>
-      <c r="N9" s="48" t="n"/>
-      <c r="O9" s="48">
-        <f>SUM(C9:N9)</f>
-        <v/>
       </c>
     </row>
     <row r="10" ht="10.5" customHeight="1" s="28">
@@ -1020,7 +996,7 @@
       </c>
       <c r="B10" s="47" t="inlineStr">
         <is>
-          <t>질병사망</t>
+          <t>일반사망</t>
         </is>
       </c>
       <c r="C10" s="48" t="n"/>
@@ -1036,7 +1012,7 @@
       <c r="M10" s="48" t="n"/>
       <c r="N10" s="48" t="n"/>
       <c r="O10" s="48">
-        <f>SUM(C10:N10)</f>
+        <f>SUM(C9:N9)</f>
         <v/>
       </c>
     </row>
@@ -1048,7 +1024,7 @@
       </c>
       <c r="B11" s="47" t="inlineStr">
         <is>
-          <t>암사망</t>
+          <t>질병사망</t>
         </is>
       </c>
       <c r="C11" s="48" t="n"/>
@@ -1064,7 +1040,7 @@
       <c r="M11" s="48" t="n"/>
       <c r="N11" s="48" t="n"/>
       <c r="O11" s="48">
-        <f>SUM(C11:N11)</f>
+        <f>SUM(C10:N10)</f>
         <v/>
       </c>
     </row>
@@ -1076,7 +1052,7 @@
       </c>
       <c r="B12" s="47" t="inlineStr">
         <is>
-          <t>상해사망</t>
+          <t>암사망</t>
         </is>
       </c>
       <c r="C12" s="48" t="n"/>
@@ -1092,19 +1068,19 @@
       <c r="M12" s="48" t="n"/>
       <c r="N12" s="48" t="n"/>
       <c r="O12" s="48">
-        <f>SUM(C12:N12)</f>
+        <f>SUM(C11:N11)</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="10.5" customHeight="1" s="28">
       <c r="A13" s="46" t="inlineStr">
         <is>
-          <t>장해</t>
+          <t>사망</t>
         </is>
       </c>
       <c r="B13" s="47" t="inlineStr">
         <is>
-          <t>상해후유장해(100%)</t>
+          <t>상해사망</t>
         </is>
       </c>
       <c r="C13" s="48" t="n"/>
@@ -1120,7 +1096,7 @@
       <c r="M13" s="48" t="n"/>
       <c r="N13" s="48" t="n"/>
       <c r="O13" s="48">
-        <f>SUM(C13:N13)</f>
+        <f>SUM(C12:N12)</f>
         <v/>
       </c>
     </row>
@@ -1132,7 +1108,7 @@
       </c>
       <c r="B14" s="47" t="inlineStr">
         <is>
-          <t>상해후유장해(3%)</t>
+          <t>상해후유장해(100%)</t>
         </is>
       </c>
       <c r="C14" s="48" t="n"/>
@@ -1148,7 +1124,7 @@
       <c r="M14" s="48" t="n"/>
       <c r="N14" s="48" t="n"/>
       <c r="O14" s="48">
-        <f>SUM(C14:N14)</f>
+        <f>SUM(C13:N13)</f>
         <v/>
       </c>
     </row>
@@ -1160,7 +1136,7 @@
       </c>
       <c r="B15" s="47" t="inlineStr">
         <is>
-          <t>질병후유장해(100%)</t>
+          <t>상해후유장해(3%)</t>
         </is>
       </c>
       <c r="C15" s="48" t="n"/>
@@ -1176,43 +1152,43 @@
       <c r="M15" s="48" t="n"/>
       <c r="N15" s="48" t="n"/>
       <c r="O15" s="48">
+        <f>SUM(C14:N14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" ht="12.75" customHeight="1" s="28">
+      <c r="A16" s="46" t="inlineStr">
+        <is>
+          <t>장해</t>
+        </is>
+      </c>
+      <c r="B16" s="47" t="inlineStr">
+        <is>
+          <t>질병후유장해(100%)</t>
+        </is>
+      </c>
+      <c r="C16" s="48" t="n"/>
+      <c r="D16" s="48" t="n"/>
+      <c r="E16" s="48" t="n"/>
+      <c r="F16" s="48" t="n"/>
+      <c r="G16" s="48" t="n"/>
+      <c r="H16" s="48" t="n"/>
+      <c r="I16" s="48" t="n"/>
+      <c r="J16" s="48" t="n"/>
+      <c r="K16" s="48" t="n"/>
+      <c r="L16" s="48" t="n"/>
+      <c r="M16" s="48" t="n"/>
+      <c r="N16" s="48" t="n"/>
+      <c r="O16" s="48">
         <f>SUM(C15:N15)</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="12.75" customHeight="1" s="28">
-      <c r="A16" s="45" t="inlineStr">
+    <row r="17" ht="10.5" customHeight="1" s="28">
+      <c r="A17" s="45" t="inlineStr">
         <is>
           <t>▶  ⊕ 암 진단</t>
         </is>
-      </c>
-    </row>
-    <row r="17" ht="10.5" customHeight="1" s="28">
-      <c r="A17" s="46" t="inlineStr">
-        <is>
-          <t>암진단</t>
-        </is>
-      </c>
-      <c r="B17" s="47" t="inlineStr">
-        <is>
-          <t>일반암 진단비</t>
-        </is>
-      </c>
-      <c r="C17" s="48" t="n"/>
-      <c r="D17" s="48" t="n"/>
-      <c r="E17" s="48" t="n"/>
-      <c r="F17" s="48" t="n"/>
-      <c r="G17" s="48" t="n"/>
-      <c r="H17" s="48" t="n"/>
-      <c r="I17" s="48" t="n"/>
-      <c r="J17" s="48" t="n"/>
-      <c r="K17" s="48" t="n"/>
-      <c r="L17" s="48" t="n"/>
-      <c r="M17" s="48" t="n"/>
-      <c r="N17" s="48" t="n"/>
-      <c r="O17" s="48">
-        <f>SUM(C17:N17)</f>
-        <v/>
       </c>
     </row>
     <row r="18" ht="10.5" customHeight="1" s="28">
@@ -1223,7 +1199,7 @@
       </c>
       <c r="B18" s="47" t="inlineStr">
         <is>
-          <t>고액암 진단비</t>
+          <t>일반암 진단비</t>
         </is>
       </c>
       <c r="C18" s="48" t="n"/>
@@ -1239,7 +1215,7 @@
       <c r="M18" s="48" t="n"/>
       <c r="N18" s="48" t="n"/>
       <c r="O18" s="48">
-        <f>SUM(C18:N18)</f>
+        <f>SUM(C17:N17)</f>
         <v/>
       </c>
     </row>
@@ -1251,7 +1227,7 @@
       </c>
       <c r="B19" s="47" t="inlineStr">
         <is>
-          <t>소액암 진단비</t>
+          <t>고액암 진단비</t>
         </is>
       </c>
       <c r="C19" s="48" t="n"/>
@@ -1267,19 +1243,19 @@
       <c r="M19" s="48" t="n"/>
       <c r="N19" s="48" t="n"/>
       <c r="O19" s="48">
-        <f>SUM(C19:N19)</f>
+        <f>SUM(C18:N18)</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="10.5" customHeight="1" s="28">
       <c r="A20" s="46" t="inlineStr">
         <is>
-          <t>말기진단</t>
+          <t>암진단</t>
         </is>
       </c>
       <c r="B20" s="47" t="inlineStr">
         <is>
-          <t>말기간질환 진단비</t>
+          <t>소액암 진단비</t>
         </is>
       </c>
       <c r="C20" s="48" t="n"/>
@@ -1295,7 +1271,7 @@
       <c r="M20" s="48" t="n"/>
       <c r="N20" s="48" t="n"/>
       <c r="O20" s="48">
-        <f>SUM(C20:N20)</f>
+        <f>SUM(C19:N19)</f>
         <v/>
       </c>
     </row>
@@ -1307,7 +1283,7 @@
       </c>
       <c r="B21" s="47" t="inlineStr">
         <is>
-          <t>말기폐질환 진단비</t>
+          <t>말기간질환 진단비</t>
         </is>
       </c>
       <c r="C21" s="48" t="n"/>
@@ -1323,7 +1299,7 @@
       <c r="M21" s="48" t="n"/>
       <c r="N21" s="48" t="n"/>
       <c r="O21" s="48">
-        <f>SUM(C21:N21)</f>
+        <f>SUM(C20:N20)</f>
         <v/>
       </c>
     </row>
@@ -1335,7 +1311,7 @@
       </c>
       <c r="B22" s="47" t="inlineStr">
         <is>
-          <t>말기신부전증 진단비</t>
+          <t>말기폐질환 진단비</t>
         </is>
       </c>
       <c r="C22" s="48" t="n"/>
@@ -1351,43 +1327,43 @@
       <c r="M22" s="48" t="n"/>
       <c r="N22" s="48" t="n"/>
       <c r="O22" s="48">
+        <f>SUM(C21:N21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="12.75" customHeight="1" s="28">
+      <c r="A23" s="46" t="inlineStr">
+        <is>
+          <t>말기진단</t>
+        </is>
+      </c>
+      <c r="B23" s="47" t="inlineStr">
+        <is>
+          <t>말기신부전증 진단비</t>
+        </is>
+      </c>
+      <c r="C23" s="48" t="n"/>
+      <c r="D23" s="48" t="n"/>
+      <c r="E23" s="48" t="n"/>
+      <c r="F23" s="48" t="n"/>
+      <c r="G23" s="48" t="n"/>
+      <c r="H23" s="48" t="n"/>
+      <c r="I23" s="48" t="n"/>
+      <c r="J23" s="48" t="n"/>
+      <c r="K23" s="48" t="n"/>
+      <c r="L23" s="48" t="n"/>
+      <c r="M23" s="48" t="n"/>
+      <c r="N23" s="48" t="n"/>
+      <c r="O23" s="48">
         <f>SUM(C22:N22)</f>
         <v/>
       </c>
     </row>
-    <row r="23" ht="12.75" customHeight="1" s="28">
-      <c r="A23" s="45" t="inlineStr">
+    <row r="24" ht="10.5" customHeight="1" s="28">
+      <c r="A24" s="45" t="inlineStr">
         <is>
           <t>▶  암 치료비 — 매년 반복 지급 (종신)</t>
         </is>
-      </c>
-    </row>
-    <row r="24" ht="10.5" customHeight="1" s="28">
-      <c r="A24" s="46" t="inlineStr">
-        <is>
-          <t>암치료</t>
-        </is>
-      </c>
-      <c r="B24" s="47" t="inlineStr">
-        <is>
-          <t>상급병원암주요치료비(수술)</t>
-        </is>
-      </c>
-      <c r="C24" s="48" t="n"/>
-      <c r="D24" s="48" t="n"/>
-      <c r="E24" s="48" t="n"/>
-      <c r="F24" s="48" t="n"/>
-      <c r="G24" s="48" t="n"/>
-      <c r="H24" s="48" t="n"/>
-      <c r="I24" s="48" t="n"/>
-      <c r="J24" s="48" t="n"/>
-      <c r="K24" s="48" t="n"/>
-      <c r="L24" s="48" t="n"/>
-      <c r="M24" s="48" t="n"/>
-      <c r="N24" s="48" t="n"/>
-      <c r="O24" s="48">
-        <f>SUM(C24:N24)</f>
-        <v/>
       </c>
     </row>
     <row r="25" ht="10.5" customHeight="1" s="28">
@@ -1398,7 +1374,7 @@
       </c>
       <c r="B25" s="47" t="inlineStr">
         <is>
-          <t>상급병원암주요치료비(방사선)</t>
+          <t>상급병원암주요치료비(수술)</t>
         </is>
       </c>
       <c r="C25" s="48" t="n"/>
@@ -1414,7 +1390,7 @@
       <c r="M25" s="48" t="n"/>
       <c r="N25" s="48" t="n"/>
       <c r="O25" s="48">
-        <f>SUM(C25:N25)</f>
+        <f>SUM(C24:N24)</f>
         <v/>
       </c>
     </row>
@@ -1426,7 +1402,7 @@
       </c>
       <c r="B26" s="47" t="inlineStr">
         <is>
-          <t>상급병원암주요치료비(약물)</t>
+          <t>상급병원암주요치료비(방사선)</t>
         </is>
       </c>
       <c r="C26" s="48" t="n"/>
@@ -1442,7 +1418,7 @@
       <c r="M26" s="48" t="n"/>
       <c r="N26" s="48" t="n"/>
       <c r="O26" s="48">
-        <f>SUM(C26:N26)</f>
+        <f>SUM(C25:N25)</f>
         <v/>
       </c>
     </row>
@@ -1454,7 +1430,7 @@
       </c>
       <c r="B27" s="47" t="inlineStr">
         <is>
-          <t>상급병원암주요치료비(복합)</t>
+          <t>상급병원암주요치료비(약물)</t>
         </is>
       </c>
       <c r="C27" s="48" t="n"/>
@@ -1470,7 +1446,7 @@
       <c r="M27" s="48" t="n"/>
       <c r="N27" s="48" t="n"/>
       <c r="O27" s="48">
-        <f>SUM(C27:N27)</f>
+        <f>SUM(C26:N26)</f>
         <v/>
       </c>
     </row>
@@ -1482,7 +1458,7 @@
       </c>
       <c r="B28" s="47" t="inlineStr">
         <is>
-          <t>종합병원비급여암주요치료비</t>
+          <t>상급병원암주요치료비(복합)</t>
         </is>
       </c>
       <c r="C28" s="48" t="n"/>
@@ -1498,7 +1474,7 @@
       <c r="M28" s="48" t="n"/>
       <c r="N28" s="48" t="n"/>
       <c r="O28" s="48">
-        <f>SUM(C28:N28)</f>
+        <f>SUM(C27:N27)</f>
         <v/>
       </c>
     </row>
@@ -1510,7 +1486,7 @@
       </c>
       <c r="B29" s="47" t="inlineStr">
         <is>
-          <t>항암방사선치료</t>
+          <t>종합병원비급여암주요치료비</t>
         </is>
       </c>
       <c r="C29" s="48" t="n"/>
@@ -1526,7 +1502,7 @@
       <c r="M29" s="48" t="n"/>
       <c r="N29" s="48" t="n"/>
       <c r="O29" s="48">
-        <f>SUM(C29:N29)</f>
+        <f>SUM(C28:N28)</f>
         <v/>
       </c>
     </row>
@@ -1538,7 +1514,7 @@
       </c>
       <c r="B30" s="47" t="inlineStr">
         <is>
-          <t>항암세기조절방사선치료</t>
+          <t>항암방사선치료</t>
         </is>
       </c>
       <c r="C30" s="48" t="n"/>
@@ -1554,7 +1530,7 @@
       <c r="M30" s="48" t="n"/>
       <c r="N30" s="48" t="n"/>
       <c r="O30" s="48">
-        <f>SUM(C30:N30)</f>
+        <f>SUM(C29:N29)</f>
         <v/>
       </c>
     </row>
@@ -1566,7 +1542,7 @@
       </c>
       <c r="B31" s="47" t="inlineStr">
         <is>
-          <t>항암양성자방사선치료</t>
+          <t>항암세기조절방사선치료</t>
         </is>
       </c>
       <c r="C31" s="48" t="n"/>
@@ -1582,7 +1558,7 @@
       <c r="M31" s="48" t="n"/>
       <c r="N31" s="48" t="n"/>
       <c r="O31" s="48">
-        <f>SUM(C31:N31)</f>
+        <f>SUM(C30:N30)</f>
         <v/>
       </c>
     </row>
@@ -1594,7 +1570,7 @@
       </c>
       <c r="B32" s="47" t="inlineStr">
         <is>
-          <t>항암약물치료</t>
+          <t>항암양성자방사선치료</t>
         </is>
       </c>
       <c r="C32" s="48" t="n"/>
@@ -1610,7 +1586,7 @@
       <c r="M32" s="48" t="n"/>
       <c r="N32" s="48" t="n"/>
       <c r="O32" s="48">
-        <f>SUM(C32:N32)</f>
+        <f>SUM(C31:N31)</f>
         <v/>
       </c>
     </row>
@@ -1622,7 +1598,7 @@
       </c>
       <c r="B33" s="47" t="inlineStr">
         <is>
-          <t>표적항암약물 허가치료</t>
+          <t>항암약물치료</t>
         </is>
       </c>
       <c r="C33" s="48" t="n"/>
@@ -1638,7 +1614,7 @@
       <c r="M33" s="48" t="n"/>
       <c r="N33" s="48" t="n"/>
       <c r="O33" s="48">
-        <f>SUM(C33:N33)</f>
+        <f>SUM(C32:N32)</f>
         <v/>
       </c>
     </row>
@@ -1648,9 +1624,9 @@
           <t>암치료</t>
         </is>
       </c>
-      <c r="B34" s="49" t="inlineStr">
-        <is>
-          <t>CAR-T 항암약물 허가치료</t>
+      <c r="B34" s="47" t="inlineStr">
+        <is>
+          <t>표적항암약물 허가치료</t>
         </is>
       </c>
       <c r="C34" s="48" t="n"/>
@@ -1666,7 +1642,7 @@
       <c r="M34" s="48" t="n"/>
       <c r="N34" s="48" t="n"/>
       <c r="O34" s="48">
-        <f>SUM(C34:N34)</f>
+        <f>SUM(C33:N33)</f>
         <v/>
       </c>
     </row>
@@ -1676,9 +1652,9 @@
           <t>암치료</t>
         </is>
       </c>
-      <c r="B35" s="47" t="inlineStr">
-        <is>
-          <t>항암호르몬약물 허가치료</t>
+      <c r="B35" s="49" t="inlineStr">
+        <is>
+          <t>CAR-T 항암약물 허가치료</t>
         </is>
       </c>
       <c r="C35" s="48" t="n"/>
@@ -1694,7 +1670,7 @@
       <c r="M35" s="48" t="n"/>
       <c r="N35" s="48" t="n"/>
       <c r="O35" s="48">
-        <f>SUM(C35:N35)</f>
+        <f>SUM(C34:N34)</f>
         <v/>
       </c>
     </row>
@@ -1706,7 +1682,7 @@
       </c>
       <c r="B36" s="47" t="inlineStr">
         <is>
-          <t>항암중입자방사선치료</t>
+          <t>항암호르몬약물 허가치료</t>
         </is>
       </c>
       <c r="C36" s="48" t="n"/>
@@ -1722,7 +1698,7 @@
       <c r="M36" s="48" t="n"/>
       <c r="N36" s="48" t="n"/>
       <c r="O36" s="48">
-        <f>SUM(C36:N36)</f>
+        <f>SUM(C35:N35)</f>
         <v/>
       </c>
     </row>
@@ -1734,7 +1710,7 @@
       </c>
       <c r="B37" s="47" t="inlineStr">
         <is>
-          <t>암직접치료상급종합병원통원</t>
+          <t>항암중입자방사선치료</t>
         </is>
       </c>
       <c r="C37" s="48" t="n"/>
@@ -1750,43 +1726,43 @@
       <c r="M37" s="48" t="n"/>
       <c r="N37" s="48" t="n"/>
       <c r="O37" s="48">
+        <f>SUM(C36:N36)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" ht="12.75" customHeight="1" s="28">
+      <c r="A38" s="46" t="inlineStr">
+        <is>
+          <t>암치료</t>
+        </is>
+      </c>
+      <c r="B38" s="47" t="inlineStr">
+        <is>
+          <t>암직접치료상급종합병원통원</t>
+        </is>
+      </c>
+      <c r="C38" s="48" t="n"/>
+      <c r="D38" s="48" t="n"/>
+      <c r="E38" s="48" t="n"/>
+      <c r="F38" s="48" t="n"/>
+      <c r="G38" s="48" t="n"/>
+      <c r="H38" s="48" t="n"/>
+      <c r="I38" s="48" t="n"/>
+      <c r="J38" s="48" t="n"/>
+      <c r="K38" s="48" t="n"/>
+      <c r="L38" s="48" t="n"/>
+      <c r="M38" s="48" t="n"/>
+      <c r="N38" s="48" t="n"/>
+      <c r="O38" s="48">
         <f>SUM(C37:N37)</f>
         <v/>
       </c>
     </row>
-    <row r="38" ht="12.75" customHeight="1" s="28">
-      <c r="A38" s="45" t="inlineStr">
+    <row r="39" ht="10.5" customHeight="1" s="28">
+      <c r="A39" s="45" t="inlineStr">
         <is>
           <t>▶  ♥ 심뇌혈관 보장</t>
         </is>
-      </c>
-    </row>
-    <row r="39" ht="10.5" customHeight="1" s="28">
-      <c r="A39" s="46" t="inlineStr">
-        <is>
-          <t>심뇌</t>
-        </is>
-      </c>
-      <c r="B39" s="47" t="inlineStr">
-        <is>
-          <t>뇌혈관질환 진단</t>
-        </is>
-      </c>
-      <c r="C39" s="48" t="n"/>
-      <c r="D39" s="48" t="n"/>
-      <c r="E39" s="48" t="n"/>
-      <c r="F39" s="48" t="n"/>
-      <c r="G39" s="48" t="n"/>
-      <c r="H39" s="48" t="n"/>
-      <c r="I39" s="48" t="n"/>
-      <c r="J39" s="48" t="n"/>
-      <c r="K39" s="48" t="n"/>
-      <c r="L39" s="48" t="n"/>
-      <c r="M39" s="48" t="n"/>
-      <c r="N39" s="48" t="n"/>
-      <c r="O39" s="48">
-        <f>SUM(C39:N39)</f>
-        <v/>
       </c>
     </row>
     <row r="40" ht="10.5" customHeight="1" s="28">
@@ -1797,7 +1773,7 @@
       </c>
       <c r="B40" s="47" t="inlineStr">
         <is>
-          <t>뇌경색증진단</t>
+          <t>뇌혈관질환 진단</t>
         </is>
       </c>
       <c r="C40" s="48" t="n"/>
@@ -1813,7 +1789,7 @@
       <c r="M40" s="48" t="n"/>
       <c r="N40" s="48" t="n"/>
       <c r="O40" s="48">
-        <f>SUM(C40:N40)</f>
+        <f>SUM(C39:N39)</f>
         <v/>
       </c>
     </row>
@@ -1825,7 +1801,7 @@
       </c>
       <c r="B41" s="47" t="inlineStr">
         <is>
-          <t>뇌출혈 진단</t>
+          <t>뇌경색증진단</t>
         </is>
       </c>
       <c r="C41" s="48" t="n"/>
@@ -1841,7 +1817,7 @@
       <c r="M41" s="48" t="n"/>
       <c r="N41" s="48" t="n"/>
       <c r="O41" s="48">
-        <f>SUM(C41:N41)</f>
+        <f>SUM(C40:N40)</f>
         <v/>
       </c>
     </row>
@@ -1853,7 +1829,7 @@
       </c>
       <c r="B42" s="47" t="inlineStr">
         <is>
-          <t>급성심근경색 진단</t>
+          <t>뇌출혈 진단</t>
         </is>
       </c>
       <c r="C42" s="48" t="n"/>
@@ -1869,7 +1845,7 @@
       <c r="M42" s="48" t="n"/>
       <c r="N42" s="48" t="n"/>
       <c r="O42" s="48">
-        <f>SUM(C42:N42)</f>
+        <f>SUM(C41:N41)</f>
         <v/>
       </c>
     </row>
@@ -1881,7 +1857,7 @@
       </c>
       <c r="B43" s="47" t="inlineStr">
         <is>
-          <t>허혈심장질환 진단</t>
+          <t>급성심근경색 진단</t>
         </is>
       </c>
       <c r="C43" s="48" t="n"/>
@@ -1897,7 +1873,7 @@
       <c r="M43" s="48" t="n"/>
       <c r="N43" s="48" t="n"/>
       <c r="O43" s="48">
-        <f>SUM(C43:N43)</f>
+        <f>SUM(C42:N42)</f>
         <v/>
       </c>
     </row>
@@ -1909,7 +1885,7 @@
       </c>
       <c r="B44" s="47" t="inlineStr">
         <is>
-          <t>순환계질환 수술 (연1회)</t>
+          <t>허혈심장질환 진단</t>
         </is>
       </c>
       <c r="C44" s="48" t="n"/>
@@ -1925,7 +1901,7 @@
       <c r="M44" s="48" t="n"/>
       <c r="N44" s="48" t="n"/>
       <c r="O44" s="48">
-        <f>SUM(C44:N44)</f>
+        <f>SUM(C43:N43)</f>
         <v/>
       </c>
     </row>
@@ -1937,7 +1913,7 @@
       </c>
       <c r="B45" s="47" t="inlineStr">
         <is>
-          <t>순환계질환 혈전 용해 (연1회)</t>
+          <t>순환계질환 수술 (연1회)</t>
         </is>
       </c>
       <c r="C45" s="48" t="n"/>
@@ -1953,7 +1929,7 @@
       <c r="M45" s="48" t="n"/>
       <c r="N45" s="48" t="n"/>
       <c r="O45" s="48">
-        <f>SUM(C45:N45)</f>
+        <f>SUM(C44:N44)</f>
         <v/>
       </c>
     </row>
@@ -1965,7 +1941,7 @@
       </c>
       <c r="B46" s="47" t="inlineStr">
         <is>
-          <t>순환계질환 혈전제거 (연1회)</t>
+          <t>순환계질환 혈전 용해 (연1회)</t>
         </is>
       </c>
       <c r="C46" s="48" t="n"/>
@@ -1981,7 +1957,7 @@
       <c r="M46" s="48" t="n"/>
       <c r="N46" s="48" t="n"/>
       <c r="O46" s="48">
-        <f>SUM(C46:N46)</f>
+        <f>SUM(C45:N45)</f>
         <v/>
       </c>
     </row>
@@ -1993,7 +1969,7 @@
       </c>
       <c r="B47" s="47" t="inlineStr">
         <is>
-          <t>순환계질환 복합치료 (연1회)</t>
+          <t>순환계질환 혈전제거 (연1회)</t>
         </is>
       </c>
       <c r="C47" s="48" t="n"/>
@@ -2009,7 +1985,7 @@
       <c r="M47" s="48" t="n"/>
       <c r="N47" s="48" t="n"/>
       <c r="O47" s="48">
-        <f>SUM(C47:N47)</f>
+        <f>SUM(C46:N46)</f>
         <v/>
       </c>
     </row>
@@ -2021,7 +1997,7 @@
       </c>
       <c r="B48" s="47" t="inlineStr">
         <is>
-          <t>순환계질환 중환자실 (연1회)</t>
+          <t>순환계질환 복합치료 (연1회)</t>
         </is>
       </c>
       <c r="C48" s="48" t="n"/>
@@ -2037,43 +2013,43 @@
       <c r="M48" s="48" t="n"/>
       <c r="N48" s="48" t="n"/>
       <c r="O48" s="48">
+        <f>SUM(C47:N47)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49" ht="12.75" customHeight="1" s="28">
+      <c r="A49" s="46" t="inlineStr">
+        <is>
+          <t>심뇌</t>
+        </is>
+      </c>
+      <c r="B49" s="47" t="inlineStr">
+        <is>
+          <t>순환계질환 중환자실 (연1회)</t>
+        </is>
+      </c>
+      <c r="C49" s="48" t="n"/>
+      <c r="D49" s="48" t="n"/>
+      <c r="E49" s="48" t="n"/>
+      <c r="F49" s="48" t="n"/>
+      <c r="G49" s="48" t="n"/>
+      <c r="H49" s="48" t="n"/>
+      <c r="I49" s="48" t="n"/>
+      <c r="J49" s="48" t="n"/>
+      <c r="K49" s="48" t="n"/>
+      <c r="L49" s="48" t="n"/>
+      <c r="M49" s="48" t="n"/>
+      <c r="N49" s="48" t="n"/>
+      <c r="O49" s="48">
         <f>SUM(C48:N48)</f>
         <v/>
       </c>
     </row>
-    <row r="49" ht="12.75" customHeight="1" s="28">
-      <c r="A49" s="45" t="inlineStr">
+    <row r="50" ht="10.5" customHeight="1" s="28">
+      <c r="A50" s="45" t="inlineStr">
         <is>
           <t>▶  ✚ 수술 보장</t>
         </is>
-      </c>
-    </row>
-    <row r="50" ht="10.5" customHeight="1" s="28">
-      <c r="A50" s="46" t="inlineStr">
-        <is>
-          <t>수술</t>
-        </is>
-      </c>
-      <c r="B50" s="47" t="inlineStr">
-        <is>
-          <t>질병 수술비</t>
-        </is>
-      </c>
-      <c r="C50" s="48" t="n"/>
-      <c r="D50" s="48" t="n"/>
-      <c r="E50" s="48" t="n"/>
-      <c r="F50" s="48" t="n"/>
-      <c r="G50" s="48" t="n"/>
-      <c r="H50" s="48" t="n"/>
-      <c r="I50" s="48" t="n"/>
-      <c r="J50" s="48" t="n"/>
-      <c r="K50" s="48" t="n"/>
-      <c r="L50" s="48" t="n"/>
-      <c r="M50" s="48" t="n"/>
-      <c r="N50" s="48" t="n"/>
-      <c r="O50" s="48">
-        <f>SUM(C50:N50)</f>
-        <v/>
       </c>
     </row>
     <row r="51" ht="10.5" customHeight="1" s="28">
@@ -2084,7 +2060,7 @@
       </c>
       <c r="B51" s="47" t="inlineStr">
         <is>
-          <t>상급종합병원질병수술</t>
+          <t>질병 수술비</t>
         </is>
       </c>
       <c r="C51" s="48" t="n"/>
@@ -2100,7 +2076,7 @@
       <c r="M51" s="48" t="n"/>
       <c r="N51" s="48" t="n"/>
       <c r="O51" s="48">
-        <f>SUM(C51:N51)</f>
+        <f>SUM(C50:N50)</f>
         <v/>
       </c>
     </row>
@@ -2112,7 +2088,7 @@
       </c>
       <c r="B52" s="47" t="inlineStr">
         <is>
-          <t>재해 수술비</t>
+          <t>상급종합병원질병수술</t>
         </is>
       </c>
       <c r="C52" s="48" t="n"/>
@@ -2128,7 +2104,7 @@
       <c r="M52" s="48" t="n"/>
       <c r="N52" s="48" t="n"/>
       <c r="O52" s="48">
-        <f>SUM(C52:N52)</f>
+        <f>SUM(C51:N51)</f>
         <v/>
       </c>
     </row>
@@ -2140,7 +2116,7 @@
       </c>
       <c r="B53" s="47" t="inlineStr">
         <is>
-          <t>암 수술비</t>
+          <t>재해 수술비</t>
         </is>
       </c>
       <c r="C53" s="48" t="n"/>
@@ -2156,7 +2132,7 @@
       <c r="M53" s="48" t="n"/>
       <c r="N53" s="48" t="n"/>
       <c r="O53" s="48">
-        <f>SUM(C53:N53)</f>
+        <f>SUM(C52:N52)</f>
         <v/>
       </c>
     </row>
@@ -2168,7 +2144,7 @@
       </c>
       <c r="B54" s="47" t="inlineStr">
         <is>
-          <t>뇌출혈 수술</t>
+          <t>암 수술비</t>
         </is>
       </c>
       <c r="C54" s="48" t="n"/>
@@ -2184,7 +2160,7 @@
       <c r="M54" s="48" t="n"/>
       <c r="N54" s="48" t="n"/>
       <c r="O54" s="48">
-        <f>SUM(C54:N54)</f>
+        <f>SUM(C53:N53)</f>
         <v/>
       </c>
     </row>
@@ -2196,7 +2172,7 @@
       </c>
       <c r="B55" s="47" t="inlineStr">
         <is>
-          <t>급성심근경색 수술</t>
+          <t>뇌출혈 수술</t>
         </is>
       </c>
       <c r="C55" s="48" t="n"/>
@@ -2212,7 +2188,7 @@
       <c r="M55" s="48" t="n"/>
       <c r="N55" s="48" t="n"/>
       <c r="O55" s="48">
-        <f>SUM(C55:N55)</f>
+        <f>SUM(C54:N54)</f>
         <v/>
       </c>
     </row>
@@ -2222,9 +2198,9 @@
           <t>수술</t>
         </is>
       </c>
-      <c r="B56" s="49" t="inlineStr">
-        <is>
-          <t>1-5종 수술 1종</t>
+      <c r="B56" s="47" t="inlineStr">
+        <is>
+          <t>급성심근경색 수술</t>
         </is>
       </c>
       <c r="C56" s="48" t="n"/>
@@ -2240,7 +2216,7 @@
       <c r="M56" s="48" t="n"/>
       <c r="N56" s="48" t="n"/>
       <c r="O56" s="48">
-        <f>SUM(C56:N56)</f>
+        <f>SUM(C55:N55)</f>
         <v/>
       </c>
     </row>
@@ -2252,7 +2228,7 @@
       </c>
       <c r="B57" s="49" t="inlineStr">
         <is>
-          <t>1-5종 수술 2종</t>
+          <t>1-5종 수술 1종</t>
         </is>
       </c>
       <c r="C57" s="48" t="n"/>
@@ -2268,7 +2244,7 @@
       <c r="M57" s="48" t="n"/>
       <c r="N57" s="48" t="n"/>
       <c r="O57" s="48">
-        <f>SUM(C57:N57)</f>
+        <f>SUM(C56:N56)</f>
         <v/>
       </c>
     </row>
@@ -2280,7 +2256,7 @@
       </c>
       <c r="B58" s="49" t="inlineStr">
         <is>
-          <t>1-5종 수술 3종</t>
+          <t>1-5종 수술 2종</t>
         </is>
       </c>
       <c r="C58" s="48" t="n"/>
@@ -2296,7 +2272,7 @@
       <c r="M58" s="48" t="n"/>
       <c r="N58" s="48" t="n"/>
       <c r="O58" s="48">
-        <f>SUM(C58:N58)</f>
+        <f>SUM(C57:N57)</f>
         <v/>
       </c>
     </row>
@@ -2308,7 +2284,7 @@
       </c>
       <c r="B59" s="49" t="inlineStr">
         <is>
-          <t>1-5종 수술 4종</t>
+          <t>1-5종 수술 3종</t>
         </is>
       </c>
       <c r="C59" s="48" t="n"/>
@@ -2324,7 +2300,7 @@
       <c r="M59" s="48" t="n"/>
       <c r="N59" s="48" t="n"/>
       <c r="O59" s="48">
-        <f>SUM(C59:N59)</f>
+        <f>SUM(C58:N58)</f>
         <v/>
       </c>
     </row>
@@ -2336,7 +2312,7 @@
       </c>
       <c r="B60" s="49" t="inlineStr">
         <is>
-          <t>1-5종 수술 5종</t>
+          <t>1-5종 수술 4종</t>
         </is>
       </c>
       <c r="C60" s="48" t="n"/>
@@ -2352,54 +2328,54 @@
       <c r="M60" s="48" t="n"/>
       <c r="N60" s="48" t="n"/>
       <c r="O60" s="48">
+        <f>SUM(C59:N59)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61" ht="12.75" customHeight="1" s="28">
+      <c r="A61" s="46" t="inlineStr">
+        <is>
+          <t>수술</t>
+        </is>
+      </c>
+      <c r="B61" s="49" t="inlineStr">
+        <is>
+          <t>1-5종 수술 5종</t>
+        </is>
+      </c>
+      <c r="C61" s="48" t="n"/>
+      <c r="D61" s="48" t="n"/>
+      <c r="E61" s="48" t="n"/>
+      <c r="F61" s="48" t="n"/>
+      <c r="G61" s="48" t="n"/>
+      <c r="H61" s="48" t="n"/>
+      <c r="I61" s="48" t="n"/>
+      <c r="J61" s="48" t="n"/>
+      <c r="K61" s="48" t="n"/>
+      <c r="L61" s="48" t="n"/>
+      <c r="M61" s="48" t="n"/>
+      <c r="N61" s="48" t="n"/>
+      <c r="O61" s="48">
         <f>SUM(C60:N60)</f>
         <v/>
       </c>
     </row>
-    <row r="61" ht="12.75" customHeight="1" s="28">
-      <c r="A61" s="45" t="inlineStr">
+    <row r="62" ht="10.5" customHeight="1" s="28">
+      <c r="A62" s="45" t="inlineStr">
         <is>
           <t>▶  ⊞ 실손 · 입원 · 통원 · 일당 보장</t>
         </is>
-      </c>
-    </row>
-    <row r="62" ht="10.5" customHeight="1" s="28">
-      <c r="A62" s="50" t="inlineStr">
-        <is>
-          <t>입원</t>
-        </is>
-      </c>
-      <c r="B62" s="51" t="inlineStr">
-        <is>
-          <t>질병/상해 입원 실비</t>
-        </is>
-      </c>
-      <c r="C62" s="48" t="n"/>
-      <c r="D62" s="48" t="n"/>
-      <c r="E62" s="48" t="n"/>
-      <c r="F62" s="48" t="n"/>
-      <c r="G62" s="48" t="n"/>
-      <c r="H62" s="48" t="n"/>
-      <c r="I62" s="48" t="n"/>
-      <c r="J62" s="48" t="n"/>
-      <c r="K62" s="48" t="n"/>
-      <c r="L62" s="48" t="n"/>
-      <c r="M62" s="48" t="n"/>
-      <c r="N62" s="48" t="n"/>
-      <c r="O62" s="48">
-        <f>SUM(C62:N62)</f>
-        <v/>
       </c>
     </row>
     <row r="63" ht="10.5" customHeight="1" s="28">
       <c r="A63" s="50" t="inlineStr">
         <is>
-          <t>통원</t>
+          <t>입원</t>
         </is>
       </c>
       <c r="B63" s="51" t="inlineStr">
         <is>
-          <t>질병/상해 통원 실비</t>
+          <t>질병/상해 입원 실비</t>
         </is>
       </c>
       <c r="C63" s="48" t="n"/>
@@ -2415,19 +2391,19 @@
       <c r="M63" s="48" t="n"/>
       <c r="N63" s="48" t="n"/>
       <c r="O63" s="48">
-        <f>SUM(C63:N63)</f>
+        <f>SUM(C62:N62)</f>
         <v/>
       </c>
     </row>
     <row r="64" ht="10.5" customHeight="1" s="28">
-      <c r="A64" s="46" t="inlineStr">
-        <is>
-          <t>입원</t>
-        </is>
-      </c>
-      <c r="B64" s="47" t="inlineStr">
-        <is>
-          <t>질병입원 일당</t>
+      <c r="A64" s="50" t="inlineStr">
+        <is>
+          <t>통원</t>
+        </is>
+      </c>
+      <c r="B64" s="51" t="inlineStr">
+        <is>
+          <t>질병/상해 통원 실비</t>
         </is>
       </c>
       <c r="C64" s="48" t="n"/>
@@ -2443,7 +2419,7 @@
       <c r="M64" s="48" t="n"/>
       <c r="N64" s="48" t="n"/>
       <c r="O64" s="48">
-        <f>SUM(C64:N64)</f>
+        <f>SUM(C63:N63)</f>
         <v/>
       </c>
     </row>
@@ -2455,7 +2431,7 @@
       </c>
       <c r="B65" s="47" t="inlineStr">
         <is>
-          <t>재해입원 일당</t>
+          <t>질병입원 일당</t>
         </is>
       </c>
       <c r="C65" s="48" t="n"/>
@@ -2471,7 +2447,7 @@
       <c r="M65" s="48" t="n"/>
       <c r="N65" s="48" t="n"/>
       <c r="O65" s="48">
-        <f>SUM(C65:N65)</f>
+        <f>SUM(C64:N64)</f>
         <v/>
       </c>
     </row>
@@ -2483,7 +2459,7 @@
       </c>
       <c r="B66" s="47" t="inlineStr">
         <is>
-          <t>암입원 일당</t>
+          <t>재해입원 일당</t>
         </is>
       </c>
       <c r="C66" s="48" t="n"/>
@@ -2499,7 +2475,7 @@
       <c r="M66" s="48" t="n"/>
       <c r="N66" s="48" t="n"/>
       <c r="O66" s="48">
-        <f>SUM(C66:N66)</f>
+        <f>SUM(C65:N65)</f>
         <v/>
       </c>
     </row>
@@ -2511,7 +2487,7 @@
       </c>
       <c r="B67" s="47" t="inlineStr">
         <is>
-          <t>첫날부터 상급종합병원 입원</t>
+          <t>암입원 일당</t>
         </is>
       </c>
       <c r="C67" s="48" t="n"/>
@@ -2527,7 +2503,7 @@
       <c r="M67" s="48" t="n"/>
       <c r="N67" s="48" t="n"/>
       <c r="O67" s="48">
-        <f>SUM(C67:N67)</f>
+        <f>SUM(C66:N66)</f>
         <v/>
       </c>
     </row>
@@ -2539,7 +2515,7 @@
       </c>
       <c r="B68" s="47" t="inlineStr">
         <is>
-          <t>상급종합병원 1인실 입원</t>
+          <t>첫날부터 상급종합병원 입원</t>
         </is>
       </c>
       <c r="C68" s="48" t="n"/>
@@ -2555,7 +2531,7 @@
       <c r="M68" s="48" t="n"/>
       <c r="N68" s="48" t="n"/>
       <c r="O68" s="48">
-        <f>SUM(C68:N68)</f>
+        <f>SUM(C67:N67)</f>
         <v/>
       </c>
     </row>
@@ -2567,7 +2543,7 @@
       </c>
       <c r="B69" s="47" t="inlineStr">
         <is>
-          <t>상급종합병원 2~3인실 입원</t>
+          <t>상급종합병원 1인실 입원</t>
         </is>
       </c>
       <c r="C69" s="48" t="n"/>
@@ -2583,7 +2559,7 @@
       <c r="M69" s="48" t="n"/>
       <c r="N69" s="48" t="n"/>
       <c r="O69" s="48">
-        <f>SUM(C69:N69)</f>
+        <f>SUM(C68:N68)</f>
         <v/>
       </c>
     </row>
@@ -2595,7 +2571,7 @@
       </c>
       <c r="B70" s="47" t="inlineStr">
         <is>
-          <t>종합병원상급병실 1인실 입원</t>
+          <t>상급종합병원 2~3인실 입원</t>
         </is>
       </c>
       <c r="C70" s="48" t="n"/>
@@ -2611,7 +2587,7 @@
       <c r="M70" s="48" t="n"/>
       <c r="N70" s="48" t="n"/>
       <c r="O70" s="48">
-        <f>SUM(C70:N70)</f>
+        <f>SUM(C69:N69)</f>
         <v/>
       </c>
     </row>
@@ -2623,7 +2599,7 @@
       </c>
       <c r="B71" s="47" t="inlineStr">
         <is>
-          <t>간병인사용일당 (질병)</t>
+          <t>종합병원상급병실 1인실 입원</t>
         </is>
       </c>
       <c r="C71" s="48" t="n"/>
@@ -2639,7 +2615,7 @@
       <c r="M71" s="48" t="n"/>
       <c r="N71" s="48" t="n"/>
       <c r="O71" s="48">
-        <f>SUM(C71:N71)</f>
+        <f>SUM(C70:N70)</f>
         <v/>
       </c>
     </row>
@@ -2651,7 +2627,7 @@
       </c>
       <c r="B72" s="47" t="inlineStr">
         <is>
-          <t>간병인사용일당 (상해)</t>
+          <t>간병인사용일당 (질병)</t>
         </is>
       </c>
       <c r="C72" s="48" t="n"/>
@@ -2667,151 +2643,158 @@
       <c r="M72" s="48" t="n"/>
       <c r="N72" s="48" t="n"/>
       <c r="O72" s="48">
+        <f>SUM(C71:N71)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73" ht="12.75" customHeight="1" s="28">
+      <c r="A73" s="46" t="inlineStr">
+        <is>
+          <t>입원</t>
+        </is>
+      </c>
+      <c r="B73" s="47" t="inlineStr">
+        <is>
+          <t>간병인사용일당 (상해)</t>
+        </is>
+      </c>
+      <c r="C73" s="48" t="n"/>
+      <c r="D73" s="48" t="n"/>
+      <c r="E73" s="48" t="n"/>
+      <c r="F73" s="48" t="n"/>
+      <c r="G73" s="48" t="n"/>
+      <c r="H73" s="48" t="n"/>
+      <c r="I73" s="48" t="n"/>
+      <c r="J73" s="48" t="n"/>
+      <c r="K73" s="48" t="n"/>
+      <c r="L73" s="48" t="n"/>
+      <c r="M73" s="48" t="n"/>
+      <c r="N73" s="48" t="n"/>
+      <c r="O73" s="48">
         <f>SUM(C72:N72)</f>
         <v/>
       </c>
     </row>
-    <row r="73" ht="12.75" customHeight="1" s="28">
-      <c r="A73" s="45" t="inlineStr">
+    <row r="74" ht="10.5" customHeight="1" s="28">
+      <c r="A74" s="45" t="inlineStr">
         <is>
           <t>▶  ⊞ 치료비,기타</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="10.5" customHeight="1" s="28">
-      <c r="A74" s="46" t="inlineStr">
+    <row r="75" ht="12.75" customHeight="1" s="28">
+      <c r="A75" s="46" t="inlineStr">
         <is>
           <t>기타</t>
         </is>
       </c>
-      <c r="B74" s="47" t="inlineStr">
+      <c r="B75" s="47" t="inlineStr">
         <is>
           <t>골절진단비</t>
         </is>
       </c>
-      <c r="C74" s="48" t="n"/>
-      <c r="D74" s="48" t="n"/>
-      <c r="E74" s="48" t="n"/>
-      <c r="F74" s="48" t="n"/>
-      <c r="G74" s="48" t="n"/>
-      <c r="H74" s="48" t="n"/>
-      <c r="I74" s="48" t="n"/>
-      <c r="J74" s="48" t="n"/>
-      <c r="K74" s="48" t="n"/>
-      <c r="L74" s="48" t="n"/>
-      <c r="M74" s="48" t="n"/>
-      <c r="N74" s="48" t="n"/>
-      <c r="O74" s="48">
+      <c r="C75" s="48" t="n"/>
+      <c r="D75" s="48" t="n"/>
+      <c r="E75" s="48" t="n"/>
+      <c r="F75" s="48" t="n"/>
+      <c r="G75" s="48" t="n"/>
+      <c r="H75" s="48" t="n"/>
+      <c r="I75" s="48" t="n"/>
+      <c r="J75" s="48" t="n"/>
+      <c r="K75" s="48" t="n"/>
+      <c r="L75" s="48" t="n"/>
+      <c r="M75" s="48" t="n"/>
+      <c r="N75" s="48" t="n"/>
+      <c r="O75" s="48">
         <f>SUM(C74:N74)</f>
         <v/>
       </c>
     </row>
-    <row r="75" ht="12.75" customHeight="1" s="28">
-      <c r="A75" s="45" t="inlineStr">
+    <row r="76" ht="12" customHeight="1" s="28">
+      <c r="A76" s="45" t="inlineStr">
         <is>
           <t>▶  ⊞ 납입면제 특약 (신규 다수 추가)</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="12" customHeight="1" s="28">
-      <c r="A76" s="52" t="inlineStr">
+    <row r="77" ht="15" customHeight="1" s="28">
+      <c r="A77" s="52" t="inlineStr">
         <is>
           <t>암/뇌혈관/허혈심장/상해 납입면제 특약</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="15" customHeight="1" s="28">
-      <c r="A77" s="53" t="inlineStr">
+    <row r="78" ht="3" customHeight="1" s="28">
+      <c r="A78" s="53" t="inlineStr">
         <is>
           <t>월 납입 보험료 합계</t>
         </is>
       </c>
-      <c r="C77" s="44">
+      <c r="C78" s="44">
         <f>C7*C6</f>
         <v/>
       </c>
-      <c r="D77" s="44">
+      <c r="D78" s="44">
         <f>D7*D6</f>
         <v/>
       </c>
-      <c r="E77" s="44">
+      <c r="E78" s="44">
         <f>E7*E6</f>
         <v/>
       </c>
-      <c r="F77" s="44">
+      <c r="F78" s="44">
         <f>F7*F6</f>
         <v/>
       </c>
-      <c r="G77" s="44">
+      <c r="G78" s="44">
         <f>G7*G6</f>
         <v/>
       </c>
-      <c r="H77" s="44">
+      <c r="H78" s="44">
         <f>H7*H6</f>
         <v/>
       </c>
-      <c r="I77" s="44">
+      <c r="I78" s="44">
         <f>I7*I6</f>
         <v/>
       </c>
-      <c r="J77" s="44">
+      <c r="J78" s="44">
         <f>J7*J6</f>
         <v/>
       </c>
-      <c r="K77" s="44">
+      <c r="K78" s="44">
         <f>K7*K6</f>
         <v/>
       </c>
-      <c r="L77" s="44">
+      <c r="L78" s="44">
         <f>L7*L6</f>
         <v/>
       </c>
-      <c r="M77" s="44">
+      <c r="M78" s="44">
         <f>M7*M6</f>
         <v/>
       </c>
-      <c r="N77" s="44">
+      <c r="N78" s="44">
         <f>N7*N6</f>
         <v/>
       </c>
-      <c r="O77" s="44">
+      <c r="O78" s="44">
         <f>O7*O6</f>
         <v/>
       </c>
     </row>
-    <row r="78" ht="3" customHeight="1" s="28"/>
-    <row r="79" ht="12.75" customHeight="1" s="28">
-      <c r="A79" s="54" t="inlineStr">
+    <row r="79" ht="12.75" customHeight="1" s="28"/>
+    <row r="80" ht="13.5" customHeight="1" s="28">
+      <c r="A80" s="54" t="inlineStr">
         <is>
           <t>▶  주계약 리뷰 (생명보험 주계약 확인사항)</t>
         </is>
       </c>
-    </row>
-    <row r="80" ht="13.5" customHeight="1" s="28">
-      <c r="A80" s="55" t="inlineStr">
-        <is>
-          <t>상품1</t>
-        </is>
-      </c>
-      <c r="B80" s="56" t="n"/>
-      <c r="C80" s="57" t="n"/>
-      <c r="D80" s="58" t="n"/>
-      <c r="E80" s="58" t="n"/>
-      <c r="F80" s="58" t="n"/>
-      <c r="G80" s="58" t="n"/>
-      <c r="H80" s="58" t="n"/>
-      <c r="I80" s="58" t="n"/>
-      <c r="J80" s="58" t="n"/>
-      <c r="K80" s="58" t="n"/>
-      <c r="L80" s="58" t="n"/>
-      <c r="M80" s="58" t="n"/>
-      <c r="N80" s="58" t="n"/>
-      <c r="O80" s="56" t="n"/>
     </row>
     <row r="81" ht="13.5" customHeight="1" s="28">
       <c r="A81" s="55" t="inlineStr">
         <is>
-          <t>상품2</t>
+          <t>상품1</t>
         </is>
       </c>
       <c r="B81" s="56" t="n"/>
@@ -2832,7 +2815,7 @@
     <row r="82" ht="13.5" customHeight="1" s="28">
       <c r="A82" s="55" t="inlineStr">
         <is>
-          <t>상품3</t>
+          <t>상품2</t>
         </is>
       </c>
       <c r="B82" s="56" t="n"/>
@@ -2853,7 +2836,7 @@
     <row r="83" ht="13.5" customHeight="1" s="28">
       <c r="A83" s="55" t="inlineStr">
         <is>
-          <t>상품4</t>
+          <t>상품3</t>
         </is>
       </c>
       <c r="B83" s="56" t="n"/>
@@ -2874,7 +2857,7 @@
     <row r="84" ht="13.5" customHeight="1" s="28">
       <c r="A84" s="55" t="inlineStr">
         <is>
-          <t>상품5</t>
+          <t>상품4</t>
         </is>
       </c>
       <c r="B84" s="56" t="n"/>
@@ -2895,7 +2878,7 @@
     <row r="85" ht="13.5" customHeight="1" s="28">
       <c r="A85" s="55" t="inlineStr">
         <is>
-          <t>상품6</t>
+          <t>상품5</t>
         </is>
       </c>
       <c r="B85" s="56" t="n"/>
@@ -2916,7 +2899,7 @@
     <row r="86" ht="13.5" customHeight="1" s="28">
       <c r="A86" s="55" t="inlineStr">
         <is>
-          <t>상품7</t>
+          <t>상품6</t>
         </is>
       </c>
       <c r="B86" s="56" t="n"/>
@@ -2937,7 +2920,7 @@
     <row r="87" ht="13.5" customHeight="1" s="28">
       <c r="A87" s="55" t="inlineStr">
         <is>
-          <t>상품8</t>
+          <t>상품7</t>
         </is>
       </c>
       <c r="B87" s="56" t="n"/>
@@ -2958,7 +2941,7 @@
     <row r="88" ht="13.5" customHeight="1" s="28">
       <c r="A88" s="55" t="inlineStr">
         <is>
-          <t>상품9</t>
+          <t>상품8</t>
         </is>
       </c>
       <c r="B88" s="56" t="n"/>
@@ -2979,7 +2962,7 @@
     <row r="89" ht="13.5" customHeight="1" s="28">
       <c r="A89" s="55" t="inlineStr">
         <is>
-          <t>상품10</t>
+          <t>상품9</t>
         </is>
       </c>
       <c r="B89" s="56" t="n"/>
@@ -3000,7 +2983,7 @@
     <row r="90" ht="13.5" customHeight="1" s="28">
       <c r="A90" s="55" t="inlineStr">
         <is>
-          <t>상품11</t>
+          <t>상품10</t>
         </is>
       </c>
       <c r="B90" s="56" t="n"/>
@@ -3021,7 +3004,7 @@
     <row r="91" ht="13.5" customHeight="1" s="28">
       <c r="A91" s="55" t="inlineStr">
         <is>
-          <t>상품12</t>
+          <t>상품11</t>
         </is>
       </c>
       <c r="B91" s="56" t="n"/>
@@ -3039,8 +3022,29 @@
       <c r="N91" s="58" t="n"/>
       <c r="O91" s="56" t="n"/>
     </row>
+    <row r="92">
+      <c r="A92" s="55" t="inlineStr">
+        <is>
+          <t>상품12</t>
+        </is>
+      </c>
+      <c r="B92" s="56" t="n"/>
+      <c r="C92" s="57" t="n"/>
+      <c r="D92" s="58" t="n"/>
+      <c r="E92" s="58" t="n"/>
+      <c r="F92" s="58" t="n"/>
+      <c r="G92" s="58" t="n"/>
+      <c r="H92" s="58" t="n"/>
+      <c r="I92" s="58" t="n"/>
+      <c r="J92" s="58" t="n"/>
+      <c r="K92" s="58" t="n"/>
+      <c r="L92" s="58" t="n"/>
+      <c r="M92" s="58" t="n"/>
+      <c r="N92" s="58" t="n"/>
+      <c r="O92" s="56" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="43">
+  <mergeCells count="44">
     <mergeCell ref="A16:O16"/>
     <mergeCell ref="A82:B82"/>
     <mergeCell ref="A75:O75"/>
@@ -3059,7 +3063,6 @@
     <mergeCell ref="A23:O23"/>
     <mergeCell ref="A89:B89"/>
     <mergeCell ref="C86:O86"/>
-    <mergeCell ref="A8:O8"/>
     <mergeCell ref="A80:B80"/>
     <mergeCell ref="C83:O83"/>
     <mergeCell ref="A3:B3"/>
@@ -3070,6 +3073,8 @@
     <mergeCell ref="A85:B85"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="C88:O88"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A9:O9"/>
     <mergeCell ref="C85:O85"/>
     <mergeCell ref="A91:B91"/>
     <mergeCell ref="A4:B4"/>

--- a/templates/master_template_12.xlsx
+++ b/templates/master_template_12.xlsx
@@ -772,7 +772,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O92"/>
+  <dimension ref="A1:O91"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="6" customWidth="1" style="27" min="1" max="1"/>
@@ -954,38 +954,62 @@
       <c r="N6" s="42" t="n"/>
       <c r="O6" s="42" t="n"/>
     </row>
-    <row r="7" ht="12" customHeight="1" s="28">
-      <c r="A7" s="41" t="inlineStr">
-        <is>
-          <t>보장기간</t>
-        </is>
-      </c>
-      <c r="C7" s="42" t="n"/>
-      <c r="D7" s="42" t="n"/>
-      <c r="E7" s="42" t="n"/>
-      <c r="F7" s="42" t="n"/>
-      <c r="G7" s="42" t="n"/>
-      <c r="H7" s="42" t="n"/>
-      <c r="I7" s="42" t="n"/>
-      <c r="J7" s="42" t="n"/>
-      <c r="K7" s="42" t="n"/>
-      <c r="L7" s="42" t="n"/>
-      <c r="M7" s="42" t="n"/>
-      <c r="N7" s="42" t="n"/>
-      <c r="O7" s="42" t="n"/>
+    <row r="7" ht="15" customHeight="1" s="28">
+      <c r="A7" s="43" t="inlineStr">
+        <is>
+          <t>▶  월 납입 보험료</t>
+        </is>
+      </c>
+      <c r="C7" s="44" t="n"/>
+      <c r="D7" s="44" t="n"/>
+      <c r="E7" s="44" t="n"/>
+      <c r="F7" s="44" t="n"/>
+      <c r="G7" s="44" t="n"/>
+      <c r="H7" s="44" t="n"/>
+      <c r="I7" s="44" t="n"/>
+      <c r="J7" s="44" t="n"/>
+      <c r="K7" s="44" t="n"/>
+      <c r="L7" s="44" t="n"/>
+      <c r="M7" s="44" t="n"/>
+      <c r="N7" s="44" t="n"/>
+      <c r="O7" s="44">
+        <f>SUM(C7:N7)</f>
+        <v/>
+      </c>
     </row>
     <row r="8" ht="12.75" customHeight="1" s="28">
-      <c r="A8" s="43" t="inlineStr">
-        <is>
-          <t>▶  월 납입 보험료</t>
+      <c r="A8" s="45" t="inlineStr">
+        <is>
+          <t>▶  사망 보장</t>
         </is>
       </c>
     </row>
     <row r="9" ht="10.5" customHeight="1" s="28">
-      <c r="A9" s="45" t="inlineStr">
-        <is>
-          <t>▶  사망 보장</t>
-        </is>
+      <c r="A9" s="46" t="inlineStr">
+        <is>
+          <t>사망</t>
+        </is>
+      </c>
+      <c r="B9" s="47" t="inlineStr">
+        <is>
+          <t>일반사망</t>
+        </is>
+      </c>
+      <c r="C9" s="48" t="n"/>
+      <c r="D9" s="48" t="n"/>
+      <c r="E9" s="48" t="n"/>
+      <c r="F9" s="48" t="n"/>
+      <c r="G9" s="48" t="n"/>
+      <c r="H9" s="48" t="n"/>
+      <c r="I9" s="48" t="n"/>
+      <c r="J9" s="48" t="n"/>
+      <c r="K9" s="48" t="n"/>
+      <c r="L9" s="48" t="n"/>
+      <c r="M9" s="48" t="n"/>
+      <c r="N9" s="48" t="n"/>
+      <c r="O9" s="48">
+        <f>SUM(C9:N9)</f>
+        <v/>
       </c>
     </row>
     <row r="10" ht="10.5" customHeight="1" s="28">
@@ -996,7 +1020,7 @@
       </c>
       <c r="B10" s="47" t="inlineStr">
         <is>
-          <t>일반사망</t>
+          <t>질병사망</t>
         </is>
       </c>
       <c r="C10" s="48" t="n"/>
@@ -1012,7 +1036,7 @@
       <c r="M10" s="48" t="n"/>
       <c r="N10" s="48" t="n"/>
       <c r="O10" s="48">
-        <f>SUM(C9:N9)</f>
+        <f>SUM(C10:N10)</f>
         <v/>
       </c>
     </row>
@@ -1024,7 +1048,7 @@
       </c>
       <c r="B11" s="47" t="inlineStr">
         <is>
-          <t>질병사망</t>
+          <t>암사망</t>
         </is>
       </c>
       <c r="C11" s="48" t="n"/>
@@ -1040,7 +1064,7 @@
       <c r="M11" s="48" t="n"/>
       <c r="N11" s="48" t="n"/>
       <c r="O11" s="48">
-        <f>SUM(C10:N10)</f>
+        <f>SUM(C11:N11)</f>
         <v/>
       </c>
     </row>
@@ -1052,7 +1076,7 @@
       </c>
       <c r="B12" s="47" t="inlineStr">
         <is>
-          <t>암사망</t>
+          <t>상해사망</t>
         </is>
       </c>
       <c r="C12" s="48" t="n"/>
@@ -1068,19 +1092,19 @@
       <c r="M12" s="48" t="n"/>
       <c r="N12" s="48" t="n"/>
       <c r="O12" s="48">
-        <f>SUM(C11:N11)</f>
+        <f>SUM(C12:N12)</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="10.5" customHeight="1" s="28">
       <c r="A13" s="46" t="inlineStr">
         <is>
-          <t>사망</t>
+          <t>장해</t>
         </is>
       </c>
       <c r="B13" s="47" t="inlineStr">
         <is>
-          <t>상해사망</t>
+          <t>상해후유장해(100%)</t>
         </is>
       </c>
       <c r="C13" s="48" t="n"/>
@@ -1096,7 +1120,7 @@
       <c r="M13" s="48" t="n"/>
       <c r="N13" s="48" t="n"/>
       <c r="O13" s="48">
-        <f>SUM(C12:N12)</f>
+        <f>SUM(C13:N13)</f>
         <v/>
       </c>
     </row>
@@ -1108,7 +1132,7 @@
       </c>
       <c r="B14" s="47" t="inlineStr">
         <is>
-          <t>상해후유장해(100%)</t>
+          <t>상해후유장해(3%)</t>
         </is>
       </c>
       <c r="C14" s="48" t="n"/>
@@ -1124,7 +1148,7 @@
       <c r="M14" s="48" t="n"/>
       <c r="N14" s="48" t="n"/>
       <c r="O14" s="48">
-        <f>SUM(C13:N13)</f>
+        <f>SUM(C14:N14)</f>
         <v/>
       </c>
     </row>
@@ -1136,7 +1160,7 @@
       </c>
       <c r="B15" s="47" t="inlineStr">
         <is>
-          <t>상해후유장해(3%)</t>
+          <t>질병후유장해(100%)</t>
         </is>
       </c>
       <c r="C15" s="48" t="n"/>
@@ -1152,43 +1176,43 @@
       <c r="M15" s="48" t="n"/>
       <c r="N15" s="48" t="n"/>
       <c r="O15" s="48">
-        <f>SUM(C14:N14)</f>
+        <f>SUM(C15:N15)</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="12.75" customHeight="1" s="28">
-      <c r="A16" s="46" t="inlineStr">
-        <is>
-          <t>장해</t>
-        </is>
-      </c>
-      <c r="B16" s="47" t="inlineStr">
-        <is>
-          <t>질병후유장해(100%)</t>
-        </is>
-      </c>
-      <c r="C16" s="48" t="n"/>
-      <c r="D16" s="48" t="n"/>
-      <c r="E16" s="48" t="n"/>
-      <c r="F16" s="48" t="n"/>
-      <c r="G16" s="48" t="n"/>
-      <c r="H16" s="48" t="n"/>
-      <c r="I16" s="48" t="n"/>
-      <c r="J16" s="48" t="n"/>
-      <c r="K16" s="48" t="n"/>
-      <c r="L16" s="48" t="n"/>
-      <c r="M16" s="48" t="n"/>
-      <c r="N16" s="48" t="n"/>
-      <c r="O16" s="48">
-        <f>SUM(C15:N15)</f>
-        <v/>
+      <c r="A16" s="45" t="inlineStr">
+        <is>
+          <t>▶  ⊕ 암 진단</t>
+        </is>
       </c>
     </row>
     <row r="17" ht="10.5" customHeight="1" s="28">
-      <c r="A17" s="45" t="inlineStr">
-        <is>
-          <t>▶  ⊕ 암 진단</t>
-        </is>
+      <c r="A17" s="46" t="inlineStr">
+        <is>
+          <t>암진단</t>
+        </is>
+      </c>
+      <c r="B17" s="47" t="inlineStr">
+        <is>
+          <t>일반암 진단비</t>
+        </is>
+      </c>
+      <c r="C17" s="48" t="n"/>
+      <c r="D17" s="48" t="n"/>
+      <c r="E17" s="48" t="n"/>
+      <c r="F17" s="48" t="n"/>
+      <c r="G17" s="48" t="n"/>
+      <c r="H17" s="48" t="n"/>
+      <c r="I17" s="48" t="n"/>
+      <c r="J17" s="48" t="n"/>
+      <c r="K17" s="48" t="n"/>
+      <c r="L17" s="48" t="n"/>
+      <c r="M17" s="48" t="n"/>
+      <c r="N17" s="48" t="n"/>
+      <c r="O17" s="48">
+        <f>SUM(C17:N17)</f>
+        <v/>
       </c>
     </row>
     <row r="18" ht="10.5" customHeight="1" s="28">
@@ -1199,7 +1223,7 @@
       </c>
       <c r="B18" s="47" t="inlineStr">
         <is>
-          <t>일반암 진단비</t>
+          <t>고액암 진단비</t>
         </is>
       </c>
       <c r="C18" s="48" t="n"/>
@@ -1215,7 +1239,7 @@
       <c r="M18" s="48" t="n"/>
       <c r="N18" s="48" t="n"/>
       <c r="O18" s="48">
-        <f>SUM(C17:N17)</f>
+        <f>SUM(C18:N18)</f>
         <v/>
       </c>
     </row>
@@ -1227,7 +1251,7 @@
       </c>
       <c r="B19" s="47" t="inlineStr">
         <is>
-          <t>고액암 진단비</t>
+          <t>소액암 진단비</t>
         </is>
       </c>
       <c r="C19" s="48" t="n"/>
@@ -1243,19 +1267,19 @@
       <c r="M19" s="48" t="n"/>
       <c r="N19" s="48" t="n"/>
       <c r="O19" s="48">
-        <f>SUM(C18:N18)</f>
+        <f>SUM(C19:N19)</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="10.5" customHeight="1" s="28">
       <c r="A20" s="46" t="inlineStr">
         <is>
-          <t>암진단</t>
+          <t>말기진단</t>
         </is>
       </c>
       <c r="B20" s="47" t="inlineStr">
         <is>
-          <t>소액암 진단비</t>
+          <t>말기간질환 진단비</t>
         </is>
       </c>
       <c r="C20" s="48" t="n"/>
@@ -1271,7 +1295,7 @@
       <c r="M20" s="48" t="n"/>
       <c r="N20" s="48" t="n"/>
       <c r="O20" s="48">
-        <f>SUM(C19:N19)</f>
+        <f>SUM(C20:N20)</f>
         <v/>
       </c>
     </row>
@@ -1283,7 +1307,7 @@
       </c>
       <c r="B21" s="47" t="inlineStr">
         <is>
-          <t>말기간질환 진단비</t>
+          <t>말기폐질환 진단비</t>
         </is>
       </c>
       <c r="C21" s="48" t="n"/>
@@ -1299,7 +1323,7 @@
       <c r="M21" s="48" t="n"/>
       <c r="N21" s="48" t="n"/>
       <c r="O21" s="48">
-        <f>SUM(C20:N20)</f>
+        <f>SUM(C21:N21)</f>
         <v/>
       </c>
     </row>
@@ -1311,7 +1335,7 @@
       </c>
       <c r="B22" s="47" t="inlineStr">
         <is>
-          <t>말기폐질환 진단비</t>
+          <t>말기신부전증 진단비</t>
         </is>
       </c>
       <c r="C22" s="48" t="n"/>
@@ -1327,43 +1351,43 @@
       <c r="M22" s="48" t="n"/>
       <c r="N22" s="48" t="n"/>
       <c r="O22" s="48">
-        <f>SUM(C21:N21)</f>
+        <f>SUM(C22:N22)</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="12.75" customHeight="1" s="28">
-      <c r="A23" s="46" t="inlineStr">
-        <is>
-          <t>말기진단</t>
-        </is>
-      </c>
-      <c r="B23" s="47" t="inlineStr">
-        <is>
-          <t>말기신부전증 진단비</t>
-        </is>
-      </c>
-      <c r="C23" s="48" t="n"/>
-      <c r="D23" s="48" t="n"/>
-      <c r="E23" s="48" t="n"/>
-      <c r="F23" s="48" t="n"/>
-      <c r="G23" s="48" t="n"/>
-      <c r="H23" s="48" t="n"/>
-      <c r="I23" s="48" t="n"/>
-      <c r="J23" s="48" t="n"/>
-      <c r="K23" s="48" t="n"/>
-      <c r="L23" s="48" t="n"/>
-      <c r="M23" s="48" t="n"/>
-      <c r="N23" s="48" t="n"/>
-      <c r="O23" s="48">
-        <f>SUM(C22:N22)</f>
-        <v/>
+      <c r="A23" s="45" t="inlineStr">
+        <is>
+          <t>▶  암 치료비 — 매년 반복 지급 (종신)</t>
+        </is>
       </c>
     </row>
     <row r="24" ht="10.5" customHeight="1" s="28">
-      <c r="A24" s="45" t="inlineStr">
-        <is>
-          <t>▶  암 치료비 — 매년 반복 지급 (종신)</t>
-        </is>
+      <c r="A24" s="46" t="inlineStr">
+        <is>
+          <t>암치료</t>
+        </is>
+      </c>
+      <c r="B24" s="47" t="inlineStr">
+        <is>
+          <t>상급병원암주요치료비(수술)</t>
+        </is>
+      </c>
+      <c r="C24" s="48" t="n"/>
+      <c r="D24" s="48" t="n"/>
+      <c r="E24" s="48" t="n"/>
+      <c r="F24" s="48" t="n"/>
+      <c r="G24" s="48" t="n"/>
+      <c r="H24" s="48" t="n"/>
+      <c r="I24" s="48" t="n"/>
+      <c r="J24" s="48" t="n"/>
+      <c r="K24" s="48" t="n"/>
+      <c r="L24" s="48" t="n"/>
+      <c r="M24" s="48" t="n"/>
+      <c r="N24" s="48" t="n"/>
+      <c r="O24" s="48">
+        <f>SUM(C24:N24)</f>
+        <v/>
       </c>
     </row>
     <row r="25" ht="10.5" customHeight="1" s="28">
@@ -1374,7 +1398,7 @@
       </c>
       <c r="B25" s="47" t="inlineStr">
         <is>
-          <t>상급병원암주요치료비(수술)</t>
+          <t>상급병원암주요치료비(방사선)</t>
         </is>
       </c>
       <c r="C25" s="48" t="n"/>
@@ -1390,7 +1414,7 @@
       <c r="M25" s="48" t="n"/>
       <c r="N25" s="48" t="n"/>
       <c r="O25" s="48">
-        <f>SUM(C24:N24)</f>
+        <f>SUM(C25:N25)</f>
         <v/>
       </c>
     </row>
@@ -1402,7 +1426,7 @@
       </c>
       <c r="B26" s="47" t="inlineStr">
         <is>
-          <t>상급병원암주요치료비(방사선)</t>
+          <t>상급병원암주요치료비(약물)</t>
         </is>
       </c>
       <c r="C26" s="48" t="n"/>
@@ -1418,7 +1442,7 @@
       <c r="M26" s="48" t="n"/>
       <c r="N26" s="48" t="n"/>
       <c r="O26" s="48">
-        <f>SUM(C25:N25)</f>
+        <f>SUM(C26:N26)</f>
         <v/>
       </c>
     </row>
@@ -1430,7 +1454,7 @@
       </c>
       <c r="B27" s="47" t="inlineStr">
         <is>
-          <t>상급병원암주요치료비(약물)</t>
+          <t>상급병원암주요치료비(복합)</t>
         </is>
       </c>
       <c r="C27" s="48" t="n"/>
@@ -1446,7 +1470,7 @@
       <c r="M27" s="48" t="n"/>
       <c r="N27" s="48" t="n"/>
       <c r="O27" s="48">
-        <f>SUM(C26:N26)</f>
+        <f>SUM(C27:N27)</f>
         <v/>
       </c>
     </row>
@@ -1458,7 +1482,7 @@
       </c>
       <c r="B28" s="47" t="inlineStr">
         <is>
-          <t>상급병원암주요치료비(복합)</t>
+          <t>종합병원비급여암주요치료비</t>
         </is>
       </c>
       <c r="C28" s="48" t="n"/>
@@ -1474,7 +1498,7 @@
       <c r="M28" s="48" t="n"/>
       <c r="N28" s="48" t="n"/>
       <c r="O28" s="48">
-        <f>SUM(C27:N27)</f>
+        <f>SUM(C28:N28)</f>
         <v/>
       </c>
     </row>
@@ -1486,7 +1510,7 @@
       </c>
       <c r="B29" s="47" t="inlineStr">
         <is>
-          <t>종합병원비급여암주요치료비</t>
+          <t>항암방사선치료</t>
         </is>
       </c>
       <c r="C29" s="48" t="n"/>
@@ -1502,7 +1526,7 @@
       <c r="M29" s="48" t="n"/>
       <c r="N29" s="48" t="n"/>
       <c r="O29" s="48">
-        <f>SUM(C28:N28)</f>
+        <f>SUM(C29:N29)</f>
         <v/>
       </c>
     </row>
@@ -1514,7 +1538,7 @@
       </c>
       <c r="B30" s="47" t="inlineStr">
         <is>
-          <t>항암방사선치료</t>
+          <t>항암세기조절방사선치료</t>
         </is>
       </c>
       <c r="C30" s="48" t="n"/>
@@ -1530,7 +1554,7 @@
       <c r="M30" s="48" t="n"/>
       <c r="N30" s="48" t="n"/>
       <c r="O30" s="48">
-        <f>SUM(C29:N29)</f>
+        <f>SUM(C30:N30)</f>
         <v/>
       </c>
     </row>
@@ -1542,7 +1566,7 @@
       </c>
       <c r="B31" s="47" t="inlineStr">
         <is>
-          <t>항암세기조절방사선치료</t>
+          <t>항암양성자방사선치료</t>
         </is>
       </c>
       <c r="C31" s="48" t="n"/>
@@ -1558,7 +1582,7 @@
       <c r="M31" s="48" t="n"/>
       <c r="N31" s="48" t="n"/>
       <c r="O31" s="48">
-        <f>SUM(C30:N30)</f>
+        <f>SUM(C31:N31)</f>
         <v/>
       </c>
     </row>
@@ -1570,7 +1594,7 @@
       </c>
       <c r="B32" s="47" t="inlineStr">
         <is>
-          <t>항암양성자방사선치료</t>
+          <t>항암약물치료</t>
         </is>
       </c>
       <c r="C32" s="48" t="n"/>
@@ -1586,7 +1610,7 @@
       <c r="M32" s="48" t="n"/>
       <c r="N32" s="48" t="n"/>
       <c r="O32" s="48">
-        <f>SUM(C31:N31)</f>
+        <f>SUM(C32:N32)</f>
         <v/>
       </c>
     </row>
@@ -1598,7 +1622,7 @@
       </c>
       <c r="B33" s="47" t="inlineStr">
         <is>
-          <t>항암약물치료</t>
+          <t>표적항암약물 허가치료</t>
         </is>
       </c>
       <c r="C33" s="48" t="n"/>
@@ -1614,7 +1638,7 @@
       <c r="M33" s="48" t="n"/>
       <c r="N33" s="48" t="n"/>
       <c r="O33" s="48">
-        <f>SUM(C32:N32)</f>
+        <f>SUM(C33:N33)</f>
         <v/>
       </c>
     </row>
@@ -1624,9 +1648,9 @@
           <t>암치료</t>
         </is>
       </c>
-      <c r="B34" s="47" t="inlineStr">
-        <is>
-          <t>표적항암약물 허가치료</t>
+      <c r="B34" s="49" t="inlineStr">
+        <is>
+          <t>CAR-T 항암약물 허가치료</t>
         </is>
       </c>
       <c r="C34" s="48" t="n"/>
@@ -1642,7 +1666,7 @@
       <c r="M34" s="48" t="n"/>
       <c r="N34" s="48" t="n"/>
       <c r="O34" s="48">
-        <f>SUM(C33:N33)</f>
+        <f>SUM(C34:N34)</f>
         <v/>
       </c>
     </row>
@@ -1652,9 +1676,9 @@
           <t>암치료</t>
         </is>
       </c>
-      <c r="B35" s="49" t="inlineStr">
-        <is>
-          <t>CAR-T 항암약물 허가치료</t>
+      <c r="B35" s="47" t="inlineStr">
+        <is>
+          <t>항암호르몬약물 허가치료</t>
         </is>
       </c>
       <c r="C35" s="48" t="n"/>
@@ -1670,7 +1694,7 @@
       <c r="M35" s="48" t="n"/>
       <c r="N35" s="48" t="n"/>
       <c r="O35" s="48">
-        <f>SUM(C34:N34)</f>
+        <f>SUM(C35:N35)</f>
         <v/>
       </c>
     </row>
@@ -1682,7 +1706,7 @@
       </c>
       <c r="B36" s="47" t="inlineStr">
         <is>
-          <t>항암호르몬약물 허가치료</t>
+          <t>항암중입자방사선치료</t>
         </is>
       </c>
       <c r="C36" s="48" t="n"/>
@@ -1698,7 +1722,7 @@
       <c r="M36" s="48" t="n"/>
       <c r="N36" s="48" t="n"/>
       <c r="O36" s="48">
-        <f>SUM(C35:N35)</f>
+        <f>SUM(C36:N36)</f>
         <v/>
       </c>
     </row>
@@ -1710,7 +1734,7 @@
       </c>
       <c r="B37" s="47" t="inlineStr">
         <is>
-          <t>항암중입자방사선치료</t>
+          <t>암직접치료상급종합병원통원</t>
         </is>
       </c>
       <c r="C37" s="48" t="n"/>
@@ -1726,43 +1750,43 @@
       <c r="M37" s="48" t="n"/>
       <c r="N37" s="48" t="n"/>
       <c r="O37" s="48">
-        <f>SUM(C36:N36)</f>
+        <f>SUM(C37:N37)</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="12.75" customHeight="1" s="28">
-      <c r="A38" s="46" t="inlineStr">
-        <is>
-          <t>암치료</t>
-        </is>
-      </c>
-      <c r="B38" s="47" t="inlineStr">
-        <is>
-          <t>암직접치료상급종합병원통원</t>
-        </is>
-      </c>
-      <c r="C38" s="48" t="n"/>
-      <c r="D38" s="48" t="n"/>
-      <c r="E38" s="48" t="n"/>
-      <c r="F38" s="48" t="n"/>
-      <c r="G38" s="48" t="n"/>
-      <c r="H38" s="48" t="n"/>
-      <c r="I38" s="48" t="n"/>
-      <c r="J38" s="48" t="n"/>
-      <c r="K38" s="48" t="n"/>
-      <c r="L38" s="48" t="n"/>
-      <c r="M38" s="48" t="n"/>
-      <c r="N38" s="48" t="n"/>
-      <c r="O38" s="48">
-        <f>SUM(C37:N37)</f>
-        <v/>
+      <c r="A38" s="45" t="inlineStr">
+        <is>
+          <t>▶  ♥ 심뇌혈관 보장</t>
+        </is>
       </c>
     </row>
     <row r="39" ht="10.5" customHeight="1" s="28">
-      <c r="A39" s="45" t="inlineStr">
-        <is>
-          <t>▶  ♥ 심뇌혈관 보장</t>
-        </is>
+      <c r="A39" s="46" t="inlineStr">
+        <is>
+          <t>심뇌</t>
+        </is>
+      </c>
+      <c r="B39" s="47" t="inlineStr">
+        <is>
+          <t>뇌혈관질환 진단</t>
+        </is>
+      </c>
+      <c r="C39" s="48" t="n"/>
+      <c r="D39" s="48" t="n"/>
+      <c r="E39" s="48" t="n"/>
+      <c r="F39" s="48" t="n"/>
+      <c r="G39" s="48" t="n"/>
+      <c r="H39" s="48" t="n"/>
+      <c r="I39" s="48" t="n"/>
+      <c r="J39" s="48" t="n"/>
+      <c r="K39" s="48" t="n"/>
+      <c r="L39" s="48" t="n"/>
+      <c r="M39" s="48" t="n"/>
+      <c r="N39" s="48" t="n"/>
+      <c r="O39" s="48">
+        <f>SUM(C39:N39)</f>
+        <v/>
       </c>
     </row>
     <row r="40" ht="10.5" customHeight="1" s="28">
@@ -1773,7 +1797,7 @@
       </c>
       <c r="B40" s="47" t="inlineStr">
         <is>
-          <t>뇌혈관질환 진단</t>
+          <t>뇌경색증진단</t>
         </is>
       </c>
       <c r="C40" s="48" t="n"/>
@@ -1789,7 +1813,7 @@
       <c r="M40" s="48" t="n"/>
       <c r="N40" s="48" t="n"/>
       <c r="O40" s="48">
-        <f>SUM(C39:N39)</f>
+        <f>SUM(C40:N40)</f>
         <v/>
       </c>
     </row>
@@ -1801,7 +1825,7 @@
       </c>
       <c r="B41" s="47" t="inlineStr">
         <is>
-          <t>뇌경색증진단</t>
+          <t>뇌출혈 진단</t>
         </is>
       </c>
       <c r="C41" s="48" t="n"/>
@@ -1817,7 +1841,7 @@
       <c r="M41" s="48" t="n"/>
       <c r="N41" s="48" t="n"/>
       <c r="O41" s="48">
-        <f>SUM(C40:N40)</f>
+        <f>SUM(C41:N41)</f>
         <v/>
       </c>
     </row>
@@ -1829,7 +1853,7 @@
       </c>
       <c r="B42" s="47" t="inlineStr">
         <is>
-          <t>뇌출혈 진단</t>
+          <t>급성심근경색 진단</t>
         </is>
       </c>
       <c r="C42" s="48" t="n"/>
@@ -1845,7 +1869,7 @@
       <c r="M42" s="48" t="n"/>
       <c r="N42" s="48" t="n"/>
       <c r="O42" s="48">
-        <f>SUM(C41:N41)</f>
+        <f>SUM(C42:N42)</f>
         <v/>
       </c>
     </row>
@@ -1857,7 +1881,7 @@
       </c>
       <c r="B43" s="47" t="inlineStr">
         <is>
-          <t>급성심근경색 진단</t>
+          <t>허혈심장질환 진단</t>
         </is>
       </c>
       <c r="C43" s="48" t="n"/>
@@ -1873,7 +1897,7 @@
       <c r="M43" s="48" t="n"/>
       <c r="N43" s="48" t="n"/>
       <c r="O43" s="48">
-        <f>SUM(C42:N42)</f>
+        <f>SUM(C43:N43)</f>
         <v/>
       </c>
     </row>
@@ -1885,7 +1909,7 @@
       </c>
       <c r="B44" s="47" t="inlineStr">
         <is>
-          <t>허혈심장질환 진단</t>
+          <t>순환계질환 수술 (연1회)</t>
         </is>
       </c>
       <c r="C44" s="48" t="n"/>
@@ -1901,7 +1925,7 @@
       <c r="M44" s="48" t="n"/>
       <c r="N44" s="48" t="n"/>
       <c r="O44" s="48">
-        <f>SUM(C43:N43)</f>
+        <f>SUM(C44:N44)</f>
         <v/>
       </c>
     </row>
@@ -1913,7 +1937,7 @@
       </c>
       <c r="B45" s="47" t="inlineStr">
         <is>
-          <t>순환계질환 수술 (연1회)</t>
+          <t>순환계질환 혈전 용해 (연1회)</t>
         </is>
       </c>
       <c r="C45" s="48" t="n"/>
@@ -1929,7 +1953,7 @@
       <c r="M45" s="48" t="n"/>
       <c r="N45" s="48" t="n"/>
       <c r="O45" s="48">
-        <f>SUM(C44:N44)</f>
+        <f>SUM(C45:N45)</f>
         <v/>
       </c>
     </row>
@@ -1941,7 +1965,7 @@
       </c>
       <c r="B46" s="47" t="inlineStr">
         <is>
-          <t>순환계질환 혈전 용해 (연1회)</t>
+          <t>순환계질환 혈전제거 (연1회)</t>
         </is>
       </c>
       <c r="C46" s="48" t="n"/>
@@ -1957,7 +1981,7 @@
       <c r="M46" s="48" t="n"/>
       <c r="N46" s="48" t="n"/>
       <c r="O46" s="48">
-        <f>SUM(C45:N45)</f>
+        <f>SUM(C46:N46)</f>
         <v/>
       </c>
     </row>
@@ -1969,7 +1993,7 @@
       </c>
       <c r="B47" s="47" t="inlineStr">
         <is>
-          <t>순환계질환 혈전제거 (연1회)</t>
+          <t>순환계질환 복합치료 (연1회)</t>
         </is>
       </c>
       <c r="C47" s="48" t="n"/>
@@ -1985,7 +2009,7 @@
       <c r="M47" s="48" t="n"/>
       <c r="N47" s="48" t="n"/>
       <c r="O47" s="48">
-        <f>SUM(C46:N46)</f>
+        <f>SUM(C47:N47)</f>
         <v/>
       </c>
     </row>
@@ -1997,7 +2021,7 @@
       </c>
       <c r="B48" s="47" t="inlineStr">
         <is>
-          <t>순환계질환 복합치료 (연1회)</t>
+          <t>순환계질환 중환자실 (연1회)</t>
         </is>
       </c>
       <c r="C48" s="48" t="n"/>
@@ -2013,43 +2037,43 @@
       <c r="M48" s="48" t="n"/>
       <c r="N48" s="48" t="n"/>
       <c r="O48" s="48">
-        <f>SUM(C47:N47)</f>
+        <f>SUM(C48:N48)</f>
         <v/>
       </c>
     </row>
     <row r="49" ht="12.75" customHeight="1" s="28">
-      <c r="A49" s="46" t="inlineStr">
-        <is>
-          <t>심뇌</t>
-        </is>
-      </c>
-      <c r="B49" s="47" t="inlineStr">
-        <is>
-          <t>순환계질환 중환자실 (연1회)</t>
-        </is>
-      </c>
-      <c r="C49" s="48" t="n"/>
-      <c r="D49" s="48" t="n"/>
-      <c r="E49" s="48" t="n"/>
-      <c r="F49" s="48" t="n"/>
-      <c r="G49" s="48" t="n"/>
-      <c r="H49" s="48" t="n"/>
-      <c r="I49" s="48" t="n"/>
-      <c r="J49" s="48" t="n"/>
-      <c r="K49" s="48" t="n"/>
-      <c r="L49" s="48" t="n"/>
-      <c r="M49" s="48" t="n"/>
-      <c r="N49" s="48" t="n"/>
-      <c r="O49" s="48">
-        <f>SUM(C48:N48)</f>
-        <v/>
+      <c r="A49" s="45" t="inlineStr">
+        <is>
+          <t>▶  ✚ 수술 보장</t>
+        </is>
       </c>
     </row>
     <row r="50" ht="10.5" customHeight="1" s="28">
-      <c r="A50" s="45" t="inlineStr">
-        <is>
-          <t>▶  ✚ 수술 보장</t>
-        </is>
+      <c r="A50" s="46" t="inlineStr">
+        <is>
+          <t>수술</t>
+        </is>
+      </c>
+      <c r="B50" s="47" t="inlineStr">
+        <is>
+          <t>질병 수술비</t>
+        </is>
+      </c>
+      <c r="C50" s="48" t="n"/>
+      <c r="D50" s="48" t="n"/>
+      <c r="E50" s="48" t="n"/>
+      <c r="F50" s="48" t="n"/>
+      <c r="G50" s="48" t="n"/>
+      <c r="H50" s="48" t="n"/>
+      <c r="I50" s="48" t="n"/>
+      <c r="J50" s="48" t="n"/>
+      <c r="K50" s="48" t="n"/>
+      <c r="L50" s="48" t="n"/>
+      <c r="M50" s="48" t="n"/>
+      <c r="N50" s="48" t="n"/>
+      <c r="O50" s="48">
+        <f>SUM(C50:N50)</f>
+        <v/>
       </c>
     </row>
     <row r="51" ht="10.5" customHeight="1" s="28">
@@ -2060,7 +2084,7 @@
       </c>
       <c r="B51" s="47" t="inlineStr">
         <is>
-          <t>질병 수술비</t>
+          <t>상급종합병원질병수술</t>
         </is>
       </c>
       <c r="C51" s="48" t="n"/>
@@ -2076,7 +2100,7 @@
       <c r="M51" s="48" t="n"/>
       <c r="N51" s="48" t="n"/>
       <c r="O51" s="48">
-        <f>SUM(C50:N50)</f>
+        <f>SUM(C51:N51)</f>
         <v/>
       </c>
     </row>
@@ -2088,7 +2112,7 @@
       </c>
       <c r="B52" s="47" t="inlineStr">
         <is>
-          <t>상급종합병원질병수술</t>
+          <t>재해 수술비</t>
         </is>
       </c>
       <c r="C52" s="48" t="n"/>
@@ -2104,7 +2128,7 @@
       <c r="M52" s="48" t="n"/>
       <c r="N52" s="48" t="n"/>
       <c r="O52" s="48">
-        <f>SUM(C51:N51)</f>
+        <f>SUM(C52:N52)</f>
         <v/>
       </c>
     </row>
@@ -2116,7 +2140,7 @@
       </c>
       <c r="B53" s="47" t="inlineStr">
         <is>
-          <t>재해 수술비</t>
+          <t>암 수술비</t>
         </is>
       </c>
       <c r="C53" s="48" t="n"/>
@@ -2132,7 +2156,7 @@
       <c r="M53" s="48" t="n"/>
       <c r="N53" s="48" t="n"/>
       <c r="O53" s="48">
-        <f>SUM(C52:N52)</f>
+        <f>SUM(C53:N53)</f>
         <v/>
       </c>
     </row>
@@ -2144,7 +2168,7 @@
       </c>
       <c r="B54" s="47" t="inlineStr">
         <is>
-          <t>암 수술비</t>
+          <t>뇌출혈 수술</t>
         </is>
       </c>
       <c r="C54" s="48" t="n"/>
@@ -2160,7 +2184,7 @@
       <c r="M54" s="48" t="n"/>
       <c r="N54" s="48" t="n"/>
       <c r="O54" s="48">
-        <f>SUM(C53:N53)</f>
+        <f>SUM(C54:N54)</f>
         <v/>
       </c>
     </row>
@@ -2172,7 +2196,7 @@
       </c>
       <c r="B55" s="47" t="inlineStr">
         <is>
-          <t>뇌출혈 수술</t>
+          <t>급성심근경색 수술</t>
         </is>
       </c>
       <c r="C55" s="48" t="n"/>
@@ -2188,7 +2212,7 @@
       <c r="M55" s="48" t="n"/>
       <c r="N55" s="48" t="n"/>
       <c r="O55" s="48">
-        <f>SUM(C54:N54)</f>
+        <f>SUM(C55:N55)</f>
         <v/>
       </c>
     </row>
@@ -2198,9 +2222,9 @@
           <t>수술</t>
         </is>
       </c>
-      <c r="B56" s="47" t="inlineStr">
-        <is>
-          <t>급성심근경색 수술</t>
+      <c r="B56" s="49" t="inlineStr">
+        <is>
+          <t>1-5종 수술 1종</t>
         </is>
       </c>
       <c r="C56" s="48" t="n"/>
@@ -2216,7 +2240,7 @@
       <c r="M56" s="48" t="n"/>
       <c r="N56" s="48" t="n"/>
       <c r="O56" s="48">
-        <f>SUM(C55:N55)</f>
+        <f>SUM(C56:N56)</f>
         <v/>
       </c>
     </row>
@@ -2228,7 +2252,7 @@
       </c>
       <c r="B57" s="49" t="inlineStr">
         <is>
-          <t>1-5종 수술 1종</t>
+          <t>1-5종 수술 2종</t>
         </is>
       </c>
       <c r="C57" s="48" t="n"/>
@@ -2244,7 +2268,7 @@
       <c r="M57" s="48" t="n"/>
       <c r="N57" s="48" t="n"/>
       <c r="O57" s="48">
-        <f>SUM(C56:N56)</f>
+        <f>SUM(C57:N57)</f>
         <v/>
       </c>
     </row>
@@ -2256,7 +2280,7 @@
       </c>
       <c r="B58" s="49" t="inlineStr">
         <is>
-          <t>1-5종 수술 2종</t>
+          <t>1-5종 수술 3종</t>
         </is>
       </c>
       <c r="C58" s="48" t="n"/>
@@ -2272,7 +2296,7 @@
       <c r="M58" s="48" t="n"/>
       <c r="N58" s="48" t="n"/>
       <c r="O58" s="48">
-        <f>SUM(C57:N57)</f>
+        <f>SUM(C58:N58)</f>
         <v/>
       </c>
     </row>
@@ -2284,7 +2308,7 @@
       </c>
       <c r="B59" s="49" t="inlineStr">
         <is>
-          <t>1-5종 수술 3종</t>
+          <t>1-5종 수술 4종</t>
         </is>
       </c>
       <c r="C59" s="48" t="n"/>
@@ -2300,7 +2324,7 @@
       <c r="M59" s="48" t="n"/>
       <c r="N59" s="48" t="n"/>
       <c r="O59" s="48">
-        <f>SUM(C58:N58)</f>
+        <f>SUM(C59:N59)</f>
         <v/>
       </c>
     </row>
@@ -2312,7 +2336,7 @@
       </c>
       <c r="B60" s="49" t="inlineStr">
         <is>
-          <t>1-5종 수술 4종</t>
+          <t>1-5종 수술 5종</t>
         </is>
       </c>
       <c r="C60" s="48" t="n"/>
@@ -2328,54 +2352,54 @@
       <c r="M60" s="48" t="n"/>
       <c r="N60" s="48" t="n"/>
       <c r="O60" s="48">
-        <f>SUM(C59:N59)</f>
+        <f>SUM(C60:N60)</f>
         <v/>
       </c>
     </row>
     <row r="61" ht="12.75" customHeight="1" s="28">
-      <c r="A61" s="46" t="inlineStr">
-        <is>
-          <t>수술</t>
-        </is>
-      </c>
-      <c r="B61" s="49" t="inlineStr">
-        <is>
-          <t>1-5종 수술 5종</t>
-        </is>
-      </c>
-      <c r="C61" s="48" t="n"/>
-      <c r="D61" s="48" t="n"/>
-      <c r="E61" s="48" t="n"/>
-      <c r="F61" s="48" t="n"/>
-      <c r="G61" s="48" t="n"/>
-      <c r="H61" s="48" t="n"/>
-      <c r="I61" s="48" t="n"/>
-      <c r="J61" s="48" t="n"/>
-      <c r="K61" s="48" t="n"/>
-      <c r="L61" s="48" t="n"/>
-      <c r="M61" s="48" t="n"/>
-      <c r="N61" s="48" t="n"/>
-      <c r="O61" s="48">
-        <f>SUM(C60:N60)</f>
-        <v/>
+      <c r="A61" s="45" t="inlineStr">
+        <is>
+          <t>▶  ⊞ 실손 · 입원 · 통원 · 일당 보장</t>
+        </is>
       </c>
     </row>
     <row r="62" ht="10.5" customHeight="1" s="28">
-      <c r="A62" s="45" t="inlineStr">
-        <is>
-          <t>▶  ⊞ 실손 · 입원 · 통원 · 일당 보장</t>
-        </is>
+      <c r="A62" s="50" t="inlineStr">
+        <is>
+          <t>입원</t>
+        </is>
+      </c>
+      <c r="B62" s="51" t="inlineStr">
+        <is>
+          <t>질병/상해 입원 실비</t>
+        </is>
+      </c>
+      <c r="C62" s="48" t="n"/>
+      <c r="D62" s="48" t="n"/>
+      <c r="E62" s="48" t="n"/>
+      <c r="F62" s="48" t="n"/>
+      <c r="G62" s="48" t="n"/>
+      <c r="H62" s="48" t="n"/>
+      <c r="I62" s="48" t="n"/>
+      <c r="J62" s="48" t="n"/>
+      <c r="K62" s="48" t="n"/>
+      <c r="L62" s="48" t="n"/>
+      <c r="M62" s="48" t="n"/>
+      <c r="N62" s="48" t="n"/>
+      <c r="O62" s="48">
+        <f>SUM(C62:N62)</f>
+        <v/>
       </c>
     </row>
     <row r="63" ht="10.5" customHeight="1" s="28">
       <c r="A63" s="50" t="inlineStr">
         <is>
-          <t>입원</t>
+          <t>통원</t>
         </is>
       </c>
       <c r="B63" s="51" t="inlineStr">
         <is>
-          <t>질병/상해 입원 실비</t>
+          <t>질병/상해 통원 실비</t>
         </is>
       </c>
       <c r="C63" s="48" t="n"/>
@@ -2391,19 +2415,19 @@
       <c r="M63" s="48" t="n"/>
       <c r="N63" s="48" t="n"/>
       <c r="O63" s="48">
-        <f>SUM(C62:N62)</f>
+        <f>SUM(C63:N63)</f>
         <v/>
       </c>
     </row>
     <row r="64" ht="10.5" customHeight="1" s="28">
-      <c r="A64" s="50" t="inlineStr">
-        <is>
-          <t>통원</t>
-        </is>
-      </c>
-      <c r="B64" s="51" t="inlineStr">
-        <is>
-          <t>질병/상해 통원 실비</t>
+      <c r="A64" s="46" t="inlineStr">
+        <is>
+          <t>입원</t>
+        </is>
+      </c>
+      <c r="B64" s="47" t="inlineStr">
+        <is>
+          <t>질병입원 일당</t>
         </is>
       </c>
       <c r="C64" s="48" t="n"/>
@@ -2419,7 +2443,7 @@
       <c r="M64" s="48" t="n"/>
       <c r="N64" s="48" t="n"/>
       <c r="O64" s="48">
-        <f>SUM(C63:N63)</f>
+        <f>SUM(C64:N64)</f>
         <v/>
       </c>
     </row>
@@ -2431,7 +2455,7 @@
       </c>
       <c r="B65" s="47" t="inlineStr">
         <is>
-          <t>질병입원 일당</t>
+          <t>재해입원 일당</t>
         </is>
       </c>
       <c r="C65" s="48" t="n"/>
@@ -2447,7 +2471,7 @@
       <c r="M65" s="48" t="n"/>
       <c r="N65" s="48" t="n"/>
       <c r="O65" s="48">
-        <f>SUM(C64:N64)</f>
+        <f>SUM(C65:N65)</f>
         <v/>
       </c>
     </row>
@@ -2459,7 +2483,7 @@
       </c>
       <c r="B66" s="47" t="inlineStr">
         <is>
-          <t>재해입원 일당</t>
+          <t>암입원 일당</t>
         </is>
       </c>
       <c r="C66" s="48" t="n"/>
@@ -2475,7 +2499,7 @@
       <c r="M66" s="48" t="n"/>
       <c r="N66" s="48" t="n"/>
       <c r="O66" s="48">
-        <f>SUM(C65:N65)</f>
+        <f>SUM(C66:N66)</f>
         <v/>
       </c>
     </row>
@@ -2487,7 +2511,7 @@
       </c>
       <c r="B67" s="47" t="inlineStr">
         <is>
-          <t>암입원 일당</t>
+          <t>첫날부터 상급종합병원 입원</t>
         </is>
       </c>
       <c r="C67" s="48" t="n"/>
@@ -2503,7 +2527,7 @@
       <c r="M67" s="48" t="n"/>
       <c r="N67" s="48" t="n"/>
       <c r="O67" s="48">
-        <f>SUM(C66:N66)</f>
+        <f>SUM(C67:N67)</f>
         <v/>
       </c>
     </row>
@@ -2515,7 +2539,7 @@
       </c>
       <c r="B68" s="47" t="inlineStr">
         <is>
-          <t>첫날부터 상급종합병원 입원</t>
+          <t>상급종합병원 1인실 입원</t>
         </is>
       </c>
       <c r="C68" s="48" t="n"/>
@@ -2531,7 +2555,7 @@
       <c r="M68" s="48" t="n"/>
       <c r="N68" s="48" t="n"/>
       <c r="O68" s="48">
-        <f>SUM(C67:N67)</f>
+        <f>SUM(C68:N68)</f>
         <v/>
       </c>
     </row>
@@ -2543,7 +2567,7 @@
       </c>
       <c r="B69" s="47" t="inlineStr">
         <is>
-          <t>상급종합병원 1인실 입원</t>
+          <t>상급종합병원 2~3인실 입원</t>
         </is>
       </c>
       <c r="C69" s="48" t="n"/>
@@ -2559,7 +2583,7 @@
       <c r="M69" s="48" t="n"/>
       <c r="N69" s="48" t="n"/>
       <c r="O69" s="48">
-        <f>SUM(C68:N68)</f>
+        <f>SUM(C69:N69)</f>
         <v/>
       </c>
     </row>
@@ -2571,7 +2595,7 @@
       </c>
       <c r="B70" s="47" t="inlineStr">
         <is>
-          <t>상급종합병원 2~3인실 입원</t>
+          <t>종합병원상급병실 1인실 입원</t>
         </is>
       </c>
       <c r="C70" s="48" t="n"/>
@@ -2587,7 +2611,7 @@
       <c r="M70" s="48" t="n"/>
       <c r="N70" s="48" t="n"/>
       <c r="O70" s="48">
-        <f>SUM(C69:N69)</f>
+        <f>SUM(C70:N70)</f>
         <v/>
       </c>
     </row>
@@ -2599,7 +2623,7 @@
       </c>
       <c r="B71" s="47" t="inlineStr">
         <is>
-          <t>종합병원상급병실 1인실 입원</t>
+          <t>간병인사용일당 (질병)</t>
         </is>
       </c>
       <c r="C71" s="48" t="n"/>
@@ -2615,7 +2639,7 @@
       <c r="M71" s="48" t="n"/>
       <c r="N71" s="48" t="n"/>
       <c r="O71" s="48">
-        <f>SUM(C70:N70)</f>
+        <f>SUM(C71:N71)</f>
         <v/>
       </c>
     </row>
@@ -2627,7 +2651,7 @@
       </c>
       <c r="B72" s="47" t="inlineStr">
         <is>
-          <t>간병인사용일당 (질병)</t>
+          <t>간병인사용일당 (상해)</t>
         </is>
       </c>
       <c r="C72" s="48" t="n"/>
@@ -2643,158 +2667,151 @@
       <c r="M72" s="48" t="n"/>
       <c r="N72" s="48" t="n"/>
       <c r="O72" s="48">
-        <f>SUM(C71:N71)</f>
+        <f>SUM(C72:N72)</f>
         <v/>
       </c>
     </row>
     <row r="73" ht="12.75" customHeight="1" s="28">
-      <c r="A73" s="46" t="inlineStr">
-        <is>
-          <t>입원</t>
-        </is>
-      </c>
-      <c r="B73" s="47" t="inlineStr">
-        <is>
-          <t>간병인사용일당 (상해)</t>
-        </is>
-      </c>
-      <c r="C73" s="48" t="n"/>
-      <c r="D73" s="48" t="n"/>
-      <c r="E73" s="48" t="n"/>
-      <c r="F73" s="48" t="n"/>
-      <c r="G73" s="48" t="n"/>
-      <c r="H73" s="48" t="n"/>
-      <c r="I73" s="48" t="n"/>
-      <c r="J73" s="48" t="n"/>
-      <c r="K73" s="48" t="n"/>
-      <c r="L73" s="48" t="n"/>
-      <c r="M73" s="48" t="n"/>
-      <c r="N73" s="48" t="n"/>
-      <c r="O73" s="48">
-        <f>SUM(C72:N72)</f>
-        <v/>
+      <c r="A73" s="45" t="inlineStr">
+        <is>
+          <t>▶  ⊞ 치료비,기타</t>
+        </is>
       </c>
     </row>
     <row r="74" ht="10.5" customHeight="1" s="28">
-      <c r="A74" s="45" t="inlineStr">
-        <is>
-          <t>▶  ⊞ 치료비,기타</t>
-        </is>
+      <c r="A74" s="46" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="B74" s="47" t="inlineStr">
+        <is>
+          <t>골절진단비</t>
+        </is>
+      </c>
+      <c r="C74" s="48" t="n"/>
+      <c r="D74" s="48" t="n"/>
+      <c r="E74" s="48" t="n"/>
+      <c r="F74" s="48" t="n"/>
+      <c r="G74" s="48" t="n"/>
+      <c r="H74" s="48" t="n"/>
+      <c r="I74" s="48" t="n"/>
+      <c r="J74" s="48" t="n"/>
+      <c r="K74" s="48" t="n"/>
+      <c r="L74" s="48" t="n"/>
+      <c r="M74" s="48" t="n"/>
+      <c r="N74" s="48" t="n"/>
+      <c r="O74" s="48">
+        <f>SUM(C74:N74)</f>
+        <v/>
       </c>
     </row>
     <row r="75" ht="12.75" customHeight="1" s="28">
-      <c r="A75" s="46" t="inlineStr">
-        <is>
-          <t>기타</t>
-        </is>
-      </c>
-      <c r="B75" s="47" t="inlineStr">
-        <is>
-          <t>골절진단비</t>
-        </is>
-      </c>
-      <c r="C75" s="48" t="n"/>
-      <c r="D75" s="48" t="n"/>
-      <c r="E75" s="48" t="n"/>
-      <c r="F75" s="48" t="n"/>
-      <c r="G75" s="48" t="n"/>
-      <c r="H75" s="48" t="n"/>
-      <c r="I75" s="48" t="n"/>
-      <c r="J75" s="48" t="n"/>
-      <c r="K75" s="48" t="n"/>
-      <c r="L75" s="48" t="n"/>
-      <c r="M75" s="48" t="n"/>
-      <c r="N75" s="48" t="n"/>
-      <c r="O75" s="48">
-        <f>SUM(C74:N74)</f>
-        <v/>
+      <c r="A75" s="45" t="inlineStr">
+        <is>
+          <t>▶  ⊞ 납입면제 특약 (신규 다수 추가)</t>
+        </is>
       </c>
     </row>
     <row r="76" ht="12" customHeight="1" s="28">
-      <c r="A76" s="45" t="inlineStr">
-        <is>
-          <t>▶  ⊞ 납입면제 특약 (신규 다수 추가)</t>
+      <c r="A76" s="52" t="inlineStr">
+        <is>
+          <t>암/뇌혈관/허혈심장/상해 납입면제 특약</t>
         </is>
       </c>
     </row>
     <row r="77" ht="15" customHeight="1" s="28">
-      <c r="A77" s="52" t="inlineStr">
-        <is>
-          <t>암/뇌혈관/허혈심장/상해 납입면제 특약</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="3" customHeight="1" s="28">
-      <c r="A78" s="53" t="inlineStr">
+      <c r="A77" s="53" t="inlineStr">
         <is>
           <t>월 납입 보험료 합계</t>
         </is>
       </c>
-      <c r="C78" s="44">
+      <c r="C77" s="44">
         <f>C7*C6</f>
         <v/>
       </c>
-      <c r="D78" s="44">
+      <c r="D77" s="44">
         <f>D7*D6</f>
         <v/>
       </c>
-      <c r="E78" s="44">
+      <c r="E77" s="44">
         <f>E7*E6</f>
         <v/>
       </c>
-      <c r="F78" s="44">
+      <c r="F77" s="44">
         <f>F7*F6</f>
         <v/>
       </c>
-      <c r="G78" s="44">
+      <c r="G77" s="44">
         <f>G7*G6</f>
         <v/>
       </c>
-      <c r="H78" s="44">
+      <c r="H77" s="44">
         <f>H7*H6</f>
         <v/>
       </c>
-      <c r="I78" s="44">
+      <c r="I77" s="44">
         <f>I7*I6</f>
         <v/>
       </c>
-      <c r="J78" s="44">
+      <c r="J77" s="44">
         <f>J7*J6</f>
         <v/>
       </c>
-      <c r="K78" s="44">
+      <c r="K77" s="44">
         <f>K7*K6</f>
         <v/>
       </c>
-      <c r="L78" s="44">
+      <c r="L77" s="44">
         <f>L7*L6</f>
         <v/>
       </c>
-      <c r="M78" s="44">
+      <c r="M77" s="44">
         <f>M7*M6</f>
         <v/>
       </c>
-      <c r="N78" s="44">
+      <c r="N77" s="44">
         <f>N7*N6</f>
         <v/>
       </c>
-      <c r="O78" s="44">
+      <c r="O77" s="44">
         <f>O7*O6</f>
         <v/>
       </c>
     </row>
-    <row r="79" ht="12.75" customHeight="1" s="28"/>
+    <row r="78" ht="3" customHeight="1" s="28"/>
+    <row r="79" ht="12.75" customHeight="1" s="28">
+      <c r="A79" s="54" t="inlineStr">
+        <is>
+          <t>▶  주계약 리뷰 (생명보험 주계약 확인사항)</t>
+        </is>
+      </c>
+    </row>
     <row r="80" ht="13.5" customHeight="1" s="28">
-      <c r="A80" s="54" t="inlineStr">
-        <is>
-          <t>▶  주계약 리뷰 (생명보험 주계약 확인사항)</t>
-        </is>
-      </c>
+      <c r="A80" s="55" t="inlineStr">
+        <is>
+          <t>상품1</t>
+        </is>
+      </c>
+      <c r="B80" s="56" t="n"/>
+      <c r="C80" s="57" t="n"/>
+      <c r="D80" s="58" t="n"/>
+      <c r="E80" s="58" t="n"/>
+      <c r="F80" s="58" t="n"/>
+      <c r="G80" s="58" t="n"/>
+      <c r="H80" s="58" t="n"/>
+      <c r="I80" s="58" t="n"/>
+      <c r="J80" s="58" t="n"/>
+      <c r="K80" s="58" t="n"/>
+      <c r="L80" s="58" t="n"/>
+      <c r="M80" s="58" t="n"/>
+      <c r="N80" s="58" t="n"/>
+      <c r="O80" s="56" t="n"/>
     </row>
     <row r="81" ht="13.5" customHeight="1" s="28">
       <c r="A81" s="55" t="inlineStr">
         <is>
-          <t>상품1</t>
+          <t>상품2</t>
         </is>
       </c>
       <c r="B81" s="56" t="n"/>
@@ -2815,7 +2832,7 @@
     <row r="82" ht="13.5" customHeight="1" s="28">
       <c r="A82" s="55" t="inlineStr">
         <is>
-          <t>상품2</t>
+          <t>상품3</t>
         </is>
       </c>
       <c r="B82" s="56" t="n"/>
@@ -2836,7 +2853,7 @@
     <row r="83" ht="13.5" customHeight="1" s="28">
       <c r="A83" s="55" t="inlineStr">
         <is>
-          <t>상품3</t>
+          <t>상품4</t>
         </is>
       </c>
       <c r="B83" s="56" t="n"/>
@@ -2857,7 +2874,7 @@
     <row r="84" ht="13.5" customHeight="1" s="28">
       <c r="A84" s="55" t="inlineStr">
         <is>
-          <t>상품4</t>
+          <t>상품5</t>
         </is>
       </c>
       <c r="B84" s="56" t="n"/>
@@ -2878,7 +2895,7 @@
     <row r="85" ht="13.5" customHeight="1" s="28">
       <c r="A85" s="55" t="inlineStr">
         <is>
-          <t>상품5</t>
+          <t>상품6</t>
         </is>
       </c>
       <c r="B85" s="56" t="n"/>
@@ -2899,7 +2916,7 @@
     <row r="86" ht="13.5" customHeight="1" s="28">
       <c r="A86" s="55" t="inlineStr">
         <is>
-          <t>상품6</t>
+          <t>상품7</t>
         </is>
       </c>
       <c r="B86" s="56" t="n"/>
@@ -2920,7 +2937,7 @@
     <row r="87" ht="13.5" customHeight="1" s="28">
       <c r="A87" s="55" t="inlineStr">
         <is>
-          <t>상품7</t>
+          <t>상품8</t>
         </is>
       </c>
       <c r="B87" s="56" t="n"/>
@@ -2941,7 +2958,7 @@
     <row r="88" ht="13.5" customHeight="1" s="28">
       <c r="A88" s="55" t="inlineStr">
         <is>
-          <t>상품8</t>
+          <t>상품9</t>
         </is>
       </c>
       <c r="B88" s="56" t="n"/>
@@ -2962,7 +2979,7 @@
     <row r="89" ht="13.5" customHeight="1" s="28">
       <c r="A89" s="55" t="inlineStr">
         <is>
-          <t>상품9</t>
+          <t>상품10</t>
         </is>
       </c>
       <c r="B89" s="56" t="n"/>
@@ -2983,7 +3000,7 @@
     <row r="90" ht="13.5" customHeight="1" s="28">
       <c r="A90" s="55" t="inlineStr">
         <is>
-          <t>상품10</t>
+          <t>상품11</t>
         </is>
       </c>
       <c r="B90" s="56" t="n"/>
@@ -3004,7 +3021,7 @@
     <row r="91" ht="13.5" customHeight="1" s="28">
       <c r="A91" s="55" t="inlineStr">
         <is>
-          <t>상품11</t>
+          <t>상품12</t>
         </is>
       </c>
       <c r="B91" s="56" t="n"/>
@@ -3022,29 +3039,8 @@
       <c r="N91" s="58" t="n"/>
       <c r="O91" s="56" t="n"/>
     </row>
-    <row r="92">
-      <c r="A92" s="55" t="inlineStr">
-        <is>
-          <t>상품12</t>
-        </is>
-      </c>
-      <c r="B92" s="56" t="n"/>
-      <c r="C92" s="57" t="n"/>
-      <c r="D92" s="58" t="n"/>
-      <c r="E92" s="58" t="n"/>
-      <c r="F92" s="58" t="n"/>
-      <c r="G92" s="58" t="n"/>
-      <c r="H92" s="58" t="n"/>
-      <c r="I92" s="58" t="n"/>
-      <c r="J92" s="58" t="n"/>
-      <c r="K92" s="58" t="n"/>
-      <c r="L92" s="58" t="n"/>
-      <c r="M92" s="58" t="n"/>
-      <c r="N92" s="58" t="n"/>
-      <c r="O92" s="56" t="n"/>
-    </row>
   </sheetData>
-  <mergeCells count="44">
+  <mergeCells count="43">
     <mergeCell ref="A16:O16"/>
     <mergeCell ref="A82:B82"/>
     <mergeCell ref="A75:O75"/>
@@ -3063,6 +3059,7 @@
     <mergeCell ref="A23:O23"/>
     <mergeCell ref="A89:B89"/>
     <mergeCell ref="C86:O86"/>
+    <mergeCell ref="A8:O8"/>
     <mergeCell ref="A80:B80"/>
     <mergeCell ref="C83:O83"/>
     <mergeCell ref="A3:B3"/>
@@ -3073,8 +3070,6 @@
     <mergeCell ref="A85:B85"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="C88:O88"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A9:O9"/>
     <mergeCell ref="C85:O85"/>
     <mergeCell ref="A91:B91"/>
     <mergeCell ref="A4:B4"/>

--- a/templates/master_template_12.xlsx
+++ b/templates/master_template_12.xlsx
@@ -214,7 +214,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -340,6 +340,35 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFBBBBBB"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFBBBBBB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFBBBBBB"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFBBBBBB"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
@@ -351,7 +380,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -519,6 +548,11 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -772,12 +806,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O91"/>
+  <dimension ref="A1:O93"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="6" customWidth="1" style="27" min="1" max="1"/>
     <col width="26" customWidth="1" style="27" min="2" max="2"/>
-    <col width="10" customWidth="1" style="27" min="3" max="15"/>
+    <col width="15" customWidth="1" style="27" min="3" max="15"/>
+    <col width="15" customWidth="1" style="28" min="4" max="4"/>
+    <col width="15" customWidth="1" style="28" min="5" max="5"/>
+    <col width="15" customWidth="1" style="28" min="6" max="6"/>
+    <col width="15" customWidth="1" style="28" min="7" max="7"/>
+    <col width="15" customWidth="1" style="28" min="8" max="8"/>
+    <col width="15" customWidth="1" style="28" min="9" max="9"/>
+    <col width="15" customWidth="1" style="28" min="10" max="10"/>
+    <col width="15" customWidth="1" style="28" min="11" max="11"/>
+    <col width="15" customWidth="1" style="28" min="12" max="12"/>
+    <col width="15" customWidth="1" style="28" min="13" max="13"/>
+    <col width="15" customWidth="1" style="28" min="14" max="14"/>
+    <col width="15" customWidth="1" style="28" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="25.5" customHeight="1" s="28">
@@ -818,7 +864,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="30" customHeight="1" s="28">
+    <row r="3" ht="40" customHeight="1" s="28">
       <c r="A3" s="34" t="n"/>
       <c r="C3" s="35" t="inlineStr">
         <is>
@@ -2371,7 +2417,7 @@
       </c>
       <c r="B62" s="51" t="inlineStr">
         <is>
-          <t>질병/상해 입원 실비</t>
+          <t>질병 입원 실비</t>
         </is>
       </c>
       <c r="C62" s="48" t="n"/>
@@ -2394,12 +2440,12 @@
     <row r="63" ht="10.5" customHeight="1" s="28">
       <c r="A63" s="50" t="inlineStr">
         <is>
-          <t>통원</t>
+          <t>입원</t>
         </is>
       </c>
       <c r="B63" s="51" t="inlineStr">
         <is>
-          <t>질병/상해 통원 실비</t>
+          <t>상해 입원 실비</t>
         </is>
       </c>
       <c r="C63" s="48" t="n"/>
@@ -2420,14 +2466,14 @@
       </c>
     </row>
     <row r="64" ht="10.5" customHeight="1" s="28">
-      <c r="A64" s="46" t="inlineStr">
-        <is>
-          <t>입원</t>
-        </is>
-      </c>
-      <c r="B64" s="47" t="inlineStr">
-        <is>
-          <t>질병입원 일당</t>
+      <c r="A64" s="50" t="inlineStr">
+        <is>
+          <t>통원</t>
+        </is>
+      </c>
+      <c r="B64" s="51" t="inlineStr">
+        <is>
+          <t>질병 통원 실비</t>
         </is>
       </c>
       <c r="C64" s="48" t="n"/>
@@ -2442,20 +2488,17 @@
       <c r="L64" s="48" t="n"/>
       <c r="M64" s="48" t="n"/>
       <c r="N64" s="48" t="n"/>
-      <c r="O64" s="48">
-        <f>SUM(C64:N64)</f>
-        <v/>
-      </c>
+      <c r="O64" s="48" t="n"/>
     </row>
     <row r="65" ht="10.5" customHeight="1" s="28">
-      <c r="A65" s="46" t="inlineStr">
-        <is>
-          <t>입원</t>
-        </is>
-      </c>
-      <c r="B65" s="47" t="inlineStr">
-        <is>
-          <t>재해입원 일당</t>
+      <c r="A65" s="50" t="inlineStr">
+        <is>
+          <t>통원</t>
+        </is>
+      </c>
+      <c r="B65" s="51" t="inlineStr">
+        <is>
+          <t>상해 통원 실비</t>
         </is>
       </c>
       <c r="C65" s="48" t="n"/>
@@ -2470,10 +2513,7 @@
       <c r="L65" s="48" t="n"/>
       <c r="M65" s="48" t="n"/>
       <c r="N65" s="48" t="n"/>
-      <c r="O65" s="48">
-        <f>SUM(C65:N65)</f>
-        <v/>
-      </c>
+      <c r="O65" s="48" t="n"/>
     </row>
     <row r="66" ht="10.5" customHeight="1" s="28">
       <c r="A66" s="46" t="inlineStr">
@@ -2483,7 +2523,7 @@
       </c>
       <c r="B66" s="47" t="inlineStr">
         <is>
-          <t>암입원 일당</t>
+          <t>질병입원 일당</t>
         </is>
       </c>
       <c r="C66" s="48" t="n"/>
@@ -2499,7 +2539,7 @@
       <c r="M66" s="48" t="n"/>
       <c r="N66" s="48" t="n"/>
       <c r="O66" s="48">
-        <f>SUM(C66:N66)</f>
+        <f>SUM(C64:N64)</f>
         <v/>
       </c>
     </row>
@@ -2511,7 +2551,7 @@
       </c>
       <c r="B67" s="47" t="inlineStr">
         <is>
-          <t>첫날부터 상급종합병원 입원</t>
+          <t>재해입원 일당</t>
         </is>
       </c>
       <c r="C67" s="48" t="n"/>
@@ -2527,7 +2567,7 @@
       <c r="M67" s="48" t="n"/>
       <c r="N67" s="48" t="n"/>
       <c r="O67" s="48">
-        <f>SUM(C67:N67)</f>
+        <f>SUM(C65:N65)</f>
         <v/>
       </c>
     </row>
@@ -2539,7 +2579,7 @@
       </c>
       <c r="B68" s="47" t="inlineStr">
         <is>
-          <t>상급종합병원 1인실 입원</t>
+          <t>암입원 일당</t>
         </is>
       </c>
       <c r="C68" s="48" t="n"/>
@@ -2555,7 +2595,7 @@
       <c r="M68" s="48" t="n"/>
       <c r="N68" s="48" t="n"/>
       <c r="O68" s="48">
-        <f>SUM(C68:N68)</f>
+        <f>SUM(C66:N66)</f>
         <v/>
       </c>
     </row>
@@ -2567,7 +2607,7 @@
       </c>
       <c r="B69" s="47" t="inlineStr">
         <is>
-          <t>상급종합병원 2~3인실 입원</t>
+          <t>첫날부터 상급종합병원 입원</t>
         </is>
       </c>
       <c r="C69" s="48" t="n"/>
@@ -2583,7 +2623,7 @@
       <c r="M69" s="48" t="n"/>
       <c r="N69" s="48" t="n"/>
       <c r="O69" s="48">
-        <f>SUM(C69:N69)</f>
+        <f>SUM(C67:N67)</f>
         <v/>
       </c>
     </row>
@@ -2595,7 +2635,7 @@
       </c>
       <c r="B70" s="47" t="inlineStr">
         <is>
-          <t>종합병원상급병실 1인실 입원</t>
+          <t>상급종합병원 1인실 입원</t>
         </is>
       </c>
       <c r="C70" s="48" t="n"/>
@@ -2611,7 +2651,7 @@
       <c r="M70" s="48" t="n"/>
       <c r="N70" s="48" t="n"/>
       <c r="O70" s="48">
-        <f>SUM(C70:N70)</f>
+        <f>SUM(C68:N68)</f>
         <v/>
       </c>
     </row>
@@ -2623,7 +2663,7 @@
       </c>
       <c r="B71" s="47" t="inlineStr">
         <is>
-          <t>간병인사용일당 (질병)</t>
+          <t>상급종합병원 2~3인실 입원</t>
         </is>
       </c>
       <c r="C71" s="48" t="n"/>
@@ -2639,7 +2679,7 @@
       <c r="M71" s="48" t="n"/>
       <c r="N71" s="48" t="n"/>
       <c r="O71" s="48">
-        <f>SUM(C71:N71)</f>
+        <f>SUM(C69:N69)</f>
         <v/>
       </c>
     </row>
@@ -2651,7 +2691,7 @@
       </c>
       <c r="B72" s="47" t="inlineStr">
         <is>
-          <t>간병인사용일당 (상해)</t>
+          <t>종합병원상급병실 1인실 입원</t>
         </is>
       </c>
       <c r="C72" s="48" t="n"/>
@@ -2667,26 +2707,44 @@
       <c r="M72" s="48" t="n"/>
       <c r="N72" s="48" t="n"/>
       <c r="O72" s="48">
-        <f>SUM(C72:N72)</f>
+        <f>SUM(C70:N70)</f>
         <v/>
       </c>
     </row>
     <row r="73" ht="12.75" customHeight="1" s="28">
-      <c r="A73" s="45" t="inlineStr">
-        <is>
-          <t>▶  ⊞ 치료비,기타</t>
-        </is>
-      </c>
+      <c r="A73" s="46" t="inlineStr">
+        <is>
+          <t>입원</t>
+        </is>
+      </c>
+      <c r="B73" s="47" t="inlineStr">
+        <is>
+          <t>간병인사용일당 (질병)</t>
+        </is>
+      </c>
+      <c r="C73" s="48" t="n"/>
+      <c r="D73" s="48" t="n"/>
+      <c r="E73" s="48" t="n"/>
+      <c r="F73" s="48" t="n"/>
+      <c r="G73" s="48" t="n"/>
+      <c r="H73" s="48" t="n"/>
+      <c r="I73" s="48" t="n"/>
+      <c r="J73" s="48" t="n"/>
+      <c r="K73" s="48" t="n"/>
+      <c r="L73" s="48" t="n"/>
+      <c r="M73" s="48" t="n"/>
+      <c r="N73" s="48" t="n"/>
+      <c r="O73" s="48" t="n"/>
     </row>
     <row r="74" ht="10.5" customHeight="1" s="28">
       <c r="A74" s="46" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>입원</t>
         </is>
       </c>
       <c r="B74" s="47" t="inlineStr">
         <is>
-          <t>골절진단비</t>
+          <t>간병인사용일당 (상해)</t>
         </is>
       </c>
       <c r="C74" s="48" t="n"/>
@@ -2702,137 +2760,89 @@
       <c r="M74" s="48" t="n"/>
       <c r="N74" s="48" t="n"/>
       <c r="O74" s="48">
-        <f>SUM(C74:N74)</f>
+        <f>SUM(C72:N72)</f>
         <v/>
       </c>
     </row>
     <row r="75" ht="12.75" customHeight="1" s="28">
       <c r="A75" s="45" t="inlineStr">
         <is>
+          <t>▶  ⊞ 치료비,기타</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="12" customHeight="1" s="28">
+      <c r="A76" s="46" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="B76" s="47" t="inlineStr">
+        <is>
+          <t>골절진단비</t>
+        </is>
+      </c>
+      <c r="C76" s="48" t="n"/>
+      <c r="D76" s="48" t="n"/>
+      <c r="E76" s="48" t="n"/>
+      <c r="F76" s="48" t="n"/>
+      <c r="G76" s="48" t="n"/>
+      <c r="H76" s="48" t="n"/>
+      <c r="I76" s="48" t="n"/>
+      <c r="J76" s="48" t="n"/>
+      <c r="K76" s="48" t="n"/>
+      <c r="L76" s="48" t="n"/>
+      <c r="M76" s="48" t="n"/>
+      <c r="N76" s="48" t="n"/>
+      <c r="O76" s="48" t="n"/>
+    </row>
+    <row r="77" ht="15" customHeight="1" s="28">
+      <c r="A77" s="45" t="inlineStr">
+        <is>
           <t>▶  ⊞ 납입면제 특약 (신규 다수 추가)</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="12" customHeight="1" s="28">
-      <c r="A76" s="52" t="inlineStr">
+    <row r="78" ht="3" customHeight="1" s="28">
+      <c r="A78" s="52" t="inlineStr">
         <is>
           <t>암/뇌혈관/허혈심장/상해 납입면제 특약</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="15" customHeight="1" s="28">
-      <c r="A77" s="53" t="inlineStr">
+    <row r="79" ht="12.75" customHeight="1" s="28">
+      <c r="A79" s="59" t="inlineStr">
         <is>
           <t>월 납입 보험료 합계</t>
         </is>
       </c>
-      <c r="C77" s="44">
-        <f>C7*C6</f>
-        <v/>
-      </c>
-      <c r="D77" s="44">
-        <f>D7*D6</f>
-        <v/>
-      </c>
-      <c r="E77" s="44">
-        <f>E7*E6</f>
-        <v/>
-      </c>
-      <c r="F77" s="44">
-        <f>F7*F6</f>
-        <v/>
-      </c>
-      <c r="G77" s="44">
-        <f>G7*G6</f>
-        <v/>
-      </c>
-      <c r="H77" s="44">
-        <f>H7*H6</f>
-        <v/>
-      </c>
-      <c r="I77" s="44">
-        <f>I7*I6</f>
-        <v/>
-      </c>
-      <c r="J77" s="44">
-        <f>J7*J6</f>
-        <v/>
-      </c>
-      <c r="K77" s="44">
-        <f>K7*K6</f>
-        <v/>
-      </c>
-      <c r="L77" s="44">
-        <f>L7*L6</f>
-        <v/>
-      </c>
-      <c r="M77" s="44">
-        <f>M7*M6</f>
-        <v/>
-      </c>
-      <c r="N77" s="44">
-        <f>N7*N6</f>
-        <v/>
-      </c>
-      <c r="O77" s="44">
-        <f>O7*O6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="78" ht="3" customHeight="1" s="28"/>
-    <row r="79" ht="12.75" customHeight="1" s="28">
-      <c r="A79" s="54" t="inlineStr">
+      <c r="B79" s="60" t="n"/>
+      <c r="C79" s="60" t="n"/>
+      <c r="D79" s="60" t="n"/>
+      <c r="E79" s="60" t="n"/>
+      <c r="F79" s="60" t="n"/>
+      <c r="G79" s="60" t="n"/>
+      <c r="H79" s="60" t="n"/>
+      <c r="I79" s="60" t="n"/>
+      <c r="J79" s="60" t="n"/>
+      <c r="K79" s="60" t="n"/>
+      <c r="L79" s="60" t="n"/>
+      <c r="M79" s="60" t="n"/>
+      <c r="N79" s="60" t="n"/>
+      <c r="O79" s="61" t="n"/>
+    </row>
+    <row r="80" ht="13.5" customHeight="1" s="28"/>
+    <row r="81" ht="13.5" customHeight="1" s="28">
+      <c r="A81" s="54" t="inlineStr">
         <is>
           <t>▶  주계약 리뷰 (생명보험 주계약 확인사항)</t>
         </is>
       </c>
-    </row>
-    <row r="80" ht="13.5" customHeight="1" s="28">
-      <c r="A80" s="55" t="inlineStr">
-        <is>
-          <t>상품1</t>
-        </is>
-      </c>
-      <c r="B80" s="56" t="n"/>
-      <c r="C80" s="57" t="n"/>
-      <c r="D80" s="58" t="n"/>
-      <c r="E80" s="58" t="n"/>
-      <c r="F80" s="58" t="n"/>
-      <c r="G80" s="58" t="n"/>
-      <c r="H80" s="58" t="n"/>
-      <c r="I80" s="58" t="n"/>
-      <c r="J80" s="58" t="n"/>
-      <c r="K80" s="58" t="n"/>
-      <c r="L80" s="58" t="n"/>
-      <c r="M80" s="58" t="n"/>
-      <c r="N80" s="58" t="n"/>
-      <c r="O80" s="56" t="n"/>
-    </row>
-    <row r="81" ht="13.5" customHeight="1" s="28">
-      <c r="A81" s="55" t="inlineStr">
-        <is>
-          <t>상품2</t>
-        </is>
-      </c>
-      <c r="B81" s="56" t="n"/>
-      <c r="C81" s="57" t="n"/>
-      <c r="D81" s="58" t="n"/>
-      <c r="E81" s="58" t="n"/>
-      <c r="F81" s="58" t="n"/>
-      <c r="G81" s="58" t="n"/>
-      <c r="H81" s="58" t="n"/>
-      <c r="I81" s="58" t="n"/>
-      <c r="J81" s="58" t="n"/>
-      <c r="K81" s="58" t="n"/>
-      <c r="L81" s="58" t="n"/>
-      <c r="M81" s="58" t="n"/>
-      <c r="N81" s="58" t="n"/>
-      <c r="O81" s="56" t="n"/>
     </row>
     <row r="82" ht="13.5" customHeight="1" s="28">
       <c r="A82" s="55" t="inlineStr">
         <is>
-          <t>상품3</t>
+          <t>상품1</t>
         </is>
       </c>
       <c r="B82" s="56" t="n"/>
@@ -2853,7 +2863,7 @@
     <row r="83" ht="13.5" customHeight="1" s="28">
       <c r="A83" s="55" t="inlineStr">
         <is>
-          <t>상품4</t>
+          <t>상품2</t>
         </is>
       </c>
       <c r="B83" s="56" t="n"/>
@@ -2874,7 +2884,7 @@
     <row r="84" ht="13.5" customHeight="1" s="28">
       <c r="A84" s="55" t="inlineStr">
         <is>
-          <t>상품5</t>
+          <t>상품3</t>
         </is>
       </c>
       <c r="B84" s="56" t="n"/>
@@ -2895,7 +2905,7 @@
     <row r="85" ht="13.5" customHeight="1" s="28">
       <c r="A85" s="55" t="inlineStr">
         <is>
-          <t>상품6</t>
+          <t>상품4</t>
         </is>
       </c>
       <c r="B85" s="56" t="n"/>
@@ -2916,7 +2926,7 @@
     <row r="86" ht="13.5" customHeight="1" s="28">
       <c r="A86" s="55" t="inlineStr">
         <is>
-          <t>상품7</t>
+          <t>상품5</t>
         </is>
       </c>
       <c r="B86" s="56" t="n"/>
@@ -2937,7 +2947,7 @@
     <row r="87" ht="13.5" customHeight="1" s="28">
       <c r="A87" s="55" t="inlineStr">
         <is>
-          <t>상품8</t>
+          <t>상품6</t>
         </is>
       </c>
       <c r="B87" s="56" t="n"/>
@@ -2958,7 +2968,7 @@
     <row r="88" ht="13.5" customHeight="1" s="28">
       <c r="A88" s="55" t="inlineStr">
         <is>
-          <t>상품9</t>
+          <t>상품7</t>
         </is>
       </c>
       <c r="B88" s="56" t="n"/>
@@ -2979,7 +2989,7 @@
     <row r="89" ht="13.5" customHeight="1" s="28">
       <c r="A89" s="55" t="inlineStr">
         <is>
-          <t>상품10</t>
+          <t>상품8</t>
         </is>
       </c>
       <c r="B89" s="56" t="n"/>
@@ -3000,7 +3010,7 @@
     <row r="90" ht="13.5" customHeight="1" s="28">
       <c r="A90" s="55" t="inlineStr">
         <is>
-          <t>상품11</t>
+          <t>상품9</t>
         </is>
       </c>
       <c r="B90" s="56" t="n"/>
@@ -3021,7 +3031,7 @@
     <row r="91" ht="13.5" customHeight="1" s="28">
       <c r="A91" s="55" t="inlineStr">
         <is>
-          <t>상품12</t>
+          <t>상품10</t>
         </is>
       </c>
       <c r="B91" s="56" t="n"/>
@@ -3039,8 +3049,50 @@
       <c r="N91" s="58" t="n"/>
       <c r="O91" s="56" t="n"/>
     </row>
+    <row r="92">
+      <c r="A92" s="55" t="inlineStr">
+        <is>
+          <t>상품11</t>
+        </is>
+      </c>
+      <c r="B92" s="56" t="n"/>
+      <c r="C92" s="57" t="n"/>
+      <c r="D92" s="58" t="n"/>
+      <c r="E92" s="58" t="n"/>
+      <c r="F92" s="58" t="n"/>
+      <c r="G92" s="58" t="n"/>
+      <c r="H92" s="58" t="n"/>
+      <c r="I92" s="58" t="n"/>
+      <c r="J92" s="58" t="n"/>
+      <c r="K92" s="58" t="n"/>
+      <c r="L92" s="58" t="n"/>
+      <c r="M92" s="58" t="n"/>
+      <c r="N92" s="58" t="n"/>
+      <c r="O92" s="56" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="55" t="inlineStr">
+        <is>
+          <t>상품12</t>
+        </is>
+      </c>
+      <c r="B93" s="56" t="n"/>
+      <c r="C93" s="57" t="n"/>
+      <c r="D93" s="58" t="n"/>
+      <c r="E93" s="58" t="n"/>
+      <c r="F93" s="58" t="n"/>
+      <c r="G93" s="58" t="n"/>
+      <c r="H93" s="58" t="n"/>
+      <c r="I93" s="58" t="n"/>
+      <c r="J93" s="58" t="n"/>
+      <c r="K93" s="58" t="n"/>
+      <c r="L93" s="58" t="n"/>
+      <c r="M93" s="58" t="n"/>
+      <c r="N93" s="58" t="n"/>
+      <c r="O93" s="56" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="43">
+  <mergeCells count="41">
     <mergeCell ref="A16:O16"/>
     <mergeCell ref="A82:B82"/>
     <mergeCell ref="A75:O75"/>
@@ -3053,7 +3105,6 @@
     <mergeCell ref="C2:N2"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A90:B90"/>
-    <mergeCell ref="A76:O76"/>
     <mergeCell ref="C87:O87"/>
     <mergeCell ref="A84:B84"/>
     <mergeCell ref="A23:O23"/>
@@ -3074,7 +3125,6 @@
     <mergeCell ref="A91:B91"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="C84:O84"/>
-    <mergeCell ref="A73:O73"/>
     <mergeCell ref="C80:O80"/>
     <mergeCell ref="A81:B81"/>
     <mergeCell ref="A49:O49"/>

--- a/templates/master_template_12.xlsx
+++ b/templates/master_template_12.xlsx
@@ -2445,7 +2445,7 @@
       </c>
       <c r="B63" s="51" t="inlineStr">
         <is>
-          <t>상해 입원 실비</t>
+          <t>재해/상해 입원 실비</t>
         </is>
       </c>
       <c r="C63" s="48" t="n"/>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="B65" s="51" t="inlineStr">
         <is>
-          <t>상해 통원 실비</t>
+          <t>재해/상해 통원 실비</t>
         </is>
       </c>
       <c r="C65" s="48" t="n"/>

--- a/templates/master_template_12.xlsx
+++ b/templates/master_template_12.xlsx
@@ -2400,7 +2400,7 @@
       </c>
       <c r="B63" s="23" t="inlineStr">
         <is>
-          <t>재해/상해 입원 실비</t>
+          <t>재해 입원 실비</t>
         </is>
       </c>
       <c r="C63" s="20" t="n"/>
@@ -2453,7 +2453,7 @@
       </c>
       <c r="B65" s="23" t="inlineStr">
         <is>
-          <t>재해/상해 통원 실비</t>
+          <t>재해 통원 실비</t>
         </is>
       </c>
       <c r="C65" s="20" t="n"/>

--- a/templates/master_template_12.xlsx
+++ b/templates/master_template_12.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -95,8 +95,14 @@
       <color rgb="FF1B2A4A"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Malgun Gothic"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="15">
+  <fills count="16">
     <fill>
       <patternFill/>
     </fill>
@@ -179,6 +185,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFDE7"/>
         <bgColor rgb="FFFFF8DC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001B2A4A"/>
+        <bgColor rgb="001B2A4A"/>
       </patternFill>
     </fill>
   </fills>
@@ -312,7 +324,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -396,6 +408,9 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -979,7 +994,7 @@
       </c>
     </row>
     <row r="8" ht="12.75" customHeight="1">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="31" t="inlineStr">
         <is>
           <t>▶  사망 보장</t>
         </is>
@@ -1182,7 +1197,7 @@
       </c>
     </row>
     <row r="16" ht="12.75" customHeight="1">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="31" t="inlineStr">
         <is>
           <t>▶  ⊕ 암 진단</t>
         </is>
@@ -1357,9 +1372,9 @@
       </c>
     </row>
     <row r="23" ht="12.75" customHeight="1">
-      <c r="A23" s="17" t="inlineStr">
-        <is>
-          <t>▶  암 치료비 — 매년 반복 지급 (종신)</t>
+      <c r="A23" s="31" t="inlineStr">
+        <is>
+          <t>▶  암 치료비</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1771,7 @@
       </c>
     </row>
     <row r="38" ht="12.75" customHeight="1">
-      <c r="A38" s="17" t="inlineStr">
+      <c r="A38" s="31" t="inlineStr">
         <is>
           <t>▶  ♥ 심뇌혈관 보장</t>
         </is>
@@ -2043,7 +2058,7 @@
       </c>
     </row>
     <row r="49" ht="12.75" customHeight="1">
-      <c r="A49" s="17" t="inlineStr">
+      <c r="A49" s="31" t="inlineStr">
         <is>
           <t>▶  ✚ 수술 보장</t>
         </is>
@@ -2358,7 +2373,7 @@
       </c>
     </row>
     <row r="61" ht="12.75" customHeight="1">
-      <c r="A61" s="17" t="inlineStr">
+      <c r="A61" s="31" t="inlineStr">
         <is>
           <t>▶  ⊞ 실손 · 입원 · 통원 · 일당 보장</t>
         </is>
@@ -2723,7 +2738,7 @@
       </c>
     </row>
     <row r="75" ht="12.75" customHeight="1">
-      <c r="A75" s="17" t="inlineStr">
+      <c r="A75" s="31" t="inlineStr">
         <is>
           <t>▶  ⊞ 치료비,기타</t>
         </is>
@@ -2758,7 +2773,7 @@
       </c>
     </row>
     <row r="77" ht="12.75" customHeight="1">
-      <c r="A77" s="17" t="inlineStr">
+      <c r="A77" s="31" t="inlineStr">
         <is>
           <t>▶  ⊞ 납입면제 특약 (신규 다수 추가)</t>
         </is>

--- a/templates/master_template_12.xlsx
+++ b/templates/master_template_12.xlsx
@@ -102,7 +102,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="16">
+  <fills count="17">
     <fill>
       <patternFill/>
     </fill>
@@ -191,6 +191,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="001B2A4A"/>
         <bgColor rgb="001B2A4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004472C4"/>
+        <bgColor rgb="004472C4"/>
       </patternFill>
     </fill>
   </fills>
@@ -324,7 +330,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -409,6 +415,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -994,7 +1003,7 @@
       </c>
     </row>
     <row r="8" ht="12.75" customHeight="1">
-      <c r="A8" s="31" t="inlineStr">
+      <c r="A8" s="32" t="inlineStr">
         <is>
           <t>▶  사망 보장</t>
         </is>
@@ -1197,7 +1206,7 @@
       </c>
     </row>
     <row r="16" ht="12.75" customHeight="1">
-      <c r="A16" s="31" t="inlineStr">
+      <c r="A16" s="32" t="inlineStr">
         <is>
           <t>▶  ⊕ 암 진단</t>
         </is>
@@ -1372,7 +1381,7 @@
       </c>
     </row>
     <row r="23" ht="12.75" customHeight="1">
-      <c r="A23" s="31" t="inlineStr">
+      <c r="A23" s="32" t="inlineStr">
         <is>
           <t>▶  암 치료비</t>
         </is>
@@ -1386,7 +1395,7 @@
       </c>
       <c r="B24" s="19" t="inlineStr">
         <is>
-          <t>상급병원암주요치료비(수술)</t>
+          <t>상급병원암주요치료비(수술) (연 1회)</t>
         </is>
       </c>
       <c r="C24" s="20" t="n"/>
@@ -1414,7 +1423,7 @@
       </c>
       <c r="B25" s="19" t="inlineStr">
         <is>
-          <t>상급병원암주요치료비(방사선)</t>
+          <t>상급병원암주요치료비(방사선) (연 1회)</t>
         </is>
       </c>
       <c r="C25" s="20" t="n"/>
@@ -1442,7 +1451,7 @@
       </c>
       <c r="B26" s="19" t="inlineStr">
         <is>
-          <t>상급병원암주요치료비(약물)</t>
+          <t>상급병원암주요치료비(약물) (연 1회)</t>
         </is>
       </c>
       <c r="C26" s="20" t="n"/>
@@ -1470,7 +1479,7 @@
       </c>
       <c r="B27" s="19" t="inlineStr">
         <is>
-          <t>상급병원암주요치료비(복합)</t>
+          <t>상급병원암주요치료비(복합) (연 1회)</t>
         </is>
       </c>
       <c r="C27" s="20" t="n"/>
@@ -1498,7 +1507,7 @@
       </c>
       <c r="B28" s="19" t="inlineStr">
         <is>
-          <t>종합병원비급여암주요치료비</t>
+          <t>종합병원비급여암주요치료비 (연 1회)</t>
         </is>
       </c>
       <c r="C28" s="20" t="n"/>
@@ -1771,7 +1780,7 @@
       </c>
     </row>
     <row r="38" ht="12.75" customHeight="1">
-      <c r="A38" s="31" t="inlineStr">
+      <c r="A38" s="32" t="inlineStr">
         <is>
           <t>▶  ♥ 심뇌혈관 보장</t>
         </is>
@@ -2058,7 +2067,7 @@
       </c>
     </row>
     <row r="49" ht="12.75" customHeight="1">
-      <c r="A49" s="31" t="inlineStr">
+      <c r="A49" s="32" t="inlineStr">
         <is>
           <t>▶  ✚ 수술 보장</t>
         </is>
@@ -2373,7 +2382,7 @@
       </c>
     </row>
     <row r="61" ht="12.75" customHeight="1">
-      <c r="A61" s="31" t="inlineStr">
+      <c r="A61" s="32" t="inlineStr">
         <is>
           <t>▶  ⊞ 실손 · 입원 · 통원 · 일당 보장</t>
         </is>
@@ -2738,7 +2747,7 @@
       </c>
     </row>
     <row r="75" ht="12.75" customHeight="1">
-      <c r="A75" s="31" t="inlineStr">
+      <c r="A75" s="32" t="inlineStr">
         <is>
           <t>▶  ⊞ 치료비,기타</t>
         </is>
@@ -2773,7 +2782,7 @@
       </c>
     </row>
     <row r="77" ht="12.75" customHeight="1">
-      <c r="A77" s="31" t="inlineStr">
+      <c r="A77" s="32" t="inlineStr">
         <is>
           <t>▶  ⊞ 납입면제 특약 (신규 다수 추가)</t>
         </is>
@@ -2847,7 +2856,7 @@
     </row>
     <row r="80" ht="3" customHeight="1"/>
     <row r="81" ht="12.75" customHeight="1">
-      <c r="A81" s="26" t="inlineStr">
+      <c r="A81" s="32" t="inlineStr">
         <is>
           <t>▶  주계약 리뷰 (생명보험 주계약 확인사항)</t>
         </is>

--- a/templates/master_template_12.xlsx
+++ b/templates/master_template_12.xlsx
@@ -102,7 +102,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="17">
+  <fills count="24">
     <fill>
       <patternFill/>
     </fill>
@@ -197,6 +197,48 @@
       <patternFill patternType="solid">
         <fgColor rgb="004472C4"/>
         <bgColor rgb="004472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002E75B6"/>
+        <bgColor rgb="002E75B6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007030A0"/>
+        <bgColor rgb="007030A0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C00000"/>
+        <bgColor rgb="00C00000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00BF4B80"/>
+        <bgColor rgb="00BF4B80"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002E8B57"/>
+        <bgColor rgb="002E8B57"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D27519"/>
+        <bgColor rgb="00D27519"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="005B7E91"/>
+        <bgColor rgb="005B7E91"/>
       </patternFill>
     </fill>
   </fills>
@@ -330,7 +372,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -418,6 +460,27 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1003,7 +1066,7 @@
       </c>
     </row>
     <row r="8" ht="12.75" customHeight="1">
-      <c r="A8" s="32" t="inlineStr">
+      <c r="A8" s="33" t="inlineStr">
         <is>
           <t>▶  사망 보장</t>
         </is>
@@ -1206,7 +1269,7 @@
       </c>
     </row>
     <row r="16" ht="12.75" customHeight="1">
-      <c r="A16" s="32" t="inlineStr">
+      <c r="A16" s="34" t="inlineStr">
         <is>
           <t>▶  ⊕ 암 진단</t>
         </is>
@@ -1381,7 +1444,7 @@
       </c>
     </row>
     <row r="23" ht="12.75" customHeight="1">
-      <c r="A23" s="32" t="inlineStr">
+      <c r="A23" s="35" t="inlineStr">
         <is>
           <t>▶  암 치료비</t>
         </is>
@@ -1780,7 +1843,7 @@
       </c>
     </row>
     <row r="38" ht="12.75" customHeight="1">
-      <c r="A38" s="32" t="inlineStr">
+      <c r="A38" s="36" t="inlineStr">
         <is>
           <t>▶  ♥ 심뇌혈관 보장</t>
         </is>
@@ -2067,7 +2130,7 @@
       </c>
     </row>
     <row r="49" ht="12.75" customHeight="1">
-      <c r="A49" s="32" t="inlineStr">
+      <c r="A49" s="37" t="inlineStr">
         <is>
           <t>▶  ✚ 수술 보장</t>
         </is>
@@ -2382,7 +2445,7 @@
       </c>
     </row>
     <row r="61" ht="12.75" customHeight="1">
-      <c r="A61" s="32" t="inlineStr">
+      <c r="A61" s="38" t="inlineStr">
         <is>
           <t>▶  ⊞ 실손 · 입원 · 통원 · 일당 보장</t>
         </is>
@@ -2747,7 +2810,7 @@
       </c>
     </row>
     <row r="75" ht="12.75" customHeight="1">
-      <c r="A75" s="32" t="inlineStr">
+      <c r="A75" s="39" t="inlineStr">
         <is>
           <t>▶  ⊞ 치료비,기타</t>
         </is>
@@ -2856,7 +2919,7 @@
     </row>
     <row r="80" ht="3" customHeight="1"/>
     <row r="81" ht="12.75" customHeight="1">
-      <c r="A81" s="32" t="inlineStr">
+      <c r="A81" s="31" t="inlineStr">
         <is>
           <t>▶  주계약 리뷰 (생명보험 주계약 확인사항)</t>
         </is>

--- a/templates/master_template_12.xlsx
+++ b/templates/master_template_12.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="12">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -101,8 +101,19 @@
       <color rgb="00FFFFFF"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Malgun Gothic"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Malgun Gothic"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="24">
+  <fills count="28">
     <fill>
       <patternFill/>
     </fill>
@@ -241,6 +252,30 @@
         <bgColor rgb="005B7E91"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002B4C7E"/>
+        <bgColor rgb="002B4C7E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="003B6FA0"/>
+        <bgColor rgb="003B6FA0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="005A7D9A"/>
+        <bgColor rgb="005A7D9A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="006B3FA0"/>
+        <bgColor rgb="006B3FA0"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="11">
     <border>
@@ -372,7 +407,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -482,6 +517,36 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="24" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="26" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="11" fillId="27" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -869,7 +934,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="25.5" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="40" t="inlineStr">
         <is>
           <t>○○○님 (남자, 00세) · 보장 분석표</t>
         </is>
@@ -890,177 +955,177 @@
       <c r="O1" s="3" t="n"/>
     </row>
     <row r="2" ht="12.75" customHeight="1">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="41" t="inlineStr">
         <is>
           <t>가입상품</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="41" t="inlineStr">
         <is>
           <t>◀ 현 재</t>
         </is>
       </c>
-      <c r="O2" s="5" t="inlineStr">
+      <c r="O2" s="42" t="inlineStr">
         <is>
           <t>현재 합산</t>
         </is>
       </c>
     </row>
     <row r="3" ht="40" customHeight="1">
-      <c r="A3" s="6" t="n"/>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="A3" s="43" t="n"/>
+      <c r="C3" s="44" t="inlineStr">
         <is>
           <t>상품1
 (보험사)</t>
         </is>
       </c>
-      <c r="D3" s="8" t="inlineStr">
+      <c r="D3" s="44" t="inlineStr">
         <is>
           <t>상품2
 (보험사)</t>
         </is>
       </c>
-      <c r="E3" s="9" t="inlineStr">
+      <c r="E3" s="44" t="inlineStr">
         <is>
           <t>상품3
 (보험사)</t>
         </is>
       </c>
-      <c r="F3" s="7" t="inlineStr">
+      <c r="F3" s="44" t="inlineStr">
         <is>
           <t>상품4
 (보험사)</t>
         </is>
       </c>
-      <c r="G3" s="10" t="inlineStr">
+      <c r="G3" s="44" t="inlineStr">
         <is>
           <t>상품5
 (보험사)</t>
         </is>
       </c>
-      <c r="H3" s="8" t="inlineStr">
+      <c r="H3" s="44" t="inlineStr">
         <is>
           <t>상품6
 (보험사)</t>
         </is>
       </c>
-      <c r="I3" s="11" t="inlineStr">
+      <c r="I3" s="44" t="inlineStr">
         <is>
           <t>상품7
 (보험사)</t>
         </is>
       </c>
-      <c r="J3" s="7" t="inlineStr">
+      <c r="J3" s="44" t="inlineStr">
         <is>
           <t>상품8
 (보험사)</t>
         </is>
       </c>
-      <c r="K3" s="9" t="inlineStr">
+      <c r="K3" s="44" t="inlineStr">
         <is>
           <t>상품9
 (보험사)</t>
         </is>
       </c>
-      <c r="L3" s="8" t="inlineStr">
+      <c r="L3" s="44" t="inlineStr">
         <is>
           <t>상품10
 (보험사)</t>
         </is>
       </c>
-      <c r="M3" s="10" t="inlineStr">
+      <c r="M3" s="44" t="inlineStr">
         <is>
           <t>상품11
 (보험사)</t>
         </is>
       </c>
-      <c r="N3" s="7" t="inlineStr">
+      <c r="N3" s="44" t="inlineStr">
         <is>
           <t>상품12
 (보험사)</t>
         </is>
       </c>
-      <c r="O3" s="12" t="n"/>
+      <c r="O3" s="45" t="n"/>
     </row>
     <row r="4" ht="12" customHeight="1">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="46" t="inlineStr">
         <is>
           <t>가입년,월</t>
         </is>
       </c>
-      <c r="C4" s="14" t="n"/>
-      <c r="D4" s="14" t="n"/>
-      <c r="E4" s="14" t="n"/>
-      <c r="F4" s="14" t="n"/>
-      <c r="G4" s="14" t="n"/>
-      <c r="H4" s="14" t="n"/>
-      <c r="I4" s="14" t="n"/>
-      <c r="J4" s="14" t="n"/>
-      <c r="K4" s="14" t="n"/>
-      <c r="L4" s="14" t="n"/>
-      <c r="M4" s="14" t="n"/>
-      <c r="N4" s="14" t="n"/>
-      <c r="O4" s="14" t="n"/>
+      <c r="C4" s="47" t="n"/>
+      <c r="D4" s="47" t="n"/>
+      <c r="E4" s="47" t="n"/>
+      <c r="F4" s="47" t="n"/>
+      <c r="G4" s="47" t="n"/>
+      <c r="H4" s="47" t="n"/>
+      <c r="I4" s="47" t="n"/>
+      <c r="J4" s="47" t="n"/>
+      <c r="K4" s="47" t="n"/>
+      <c r="L4" s="47" t="n"/>
+      <c r="M4" s="47" t="n"/>
+      <c r="N4" s="47" t="n"/>
+      <c r="O4" s="47" t="n"/>
     </row>
     <row r="5" ht="12" customHeight="1">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="46" t="inlineStr">
         <is>
           <t>납입기간</t>
         </is>
       </c>
-      <c r="C5" s="14" t="n"/>
-      <c r="D5" s="14" t="n"/>
-      <c r="E5" s="14" t="n"/>
-      <c r="F5" s="14" t="n"/>
-      <c r="G5" s="14" t="n"/>
-      <c r="H5" s="14" t="n"/>
-      <c r="I5" s="14" t="n"/>
-      <c r="J5" s="14" t="n"/>
-      <c r="K5" s="14" t="n"/>
-      <c r="L5" s="14" t="n"/>
-      <c r="M5" s="14" t="n"/>
-      <c r="N5" s="14" t="n"/>
-      <c r="O5" s="14" t="n"/>
+      <c r="C5" s="47" t="n"/>
+      <c r="D5" s="47" t="n"/>
+      <c r="E5" s="47" t="n"/>
+      <c r="F5" s="47" t="n"/>
+      <c r="G5" s="47" t="n"/>
+      <c r="H5" s="47" t="n"/>
+      <c r="I5" s="47" t="n"/>
+      <c r="J5" s="47" t="n"/>
+      <c r="K5" s="47" t="n"/>
+      <c r="L5" s="47" t="n"/>
+      <c r="M5" s="47" t="n"/>
+      <c r="N5" s="47" t="n"/>
+      <c r="O5" s="47" t="n"/>
     </row>
     <row r="6" ht="12" customHeight="1">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="46" t="inlineStr">
         <is>
           <t>총납입개월</t>
         </is>
       </c>
-      <c r="C6" s="14" t="n"/>
-      <c r="D6" s="14" t="n"/>
-      <c r="E6" s="14" t="n"/>
-      <c r="F6" s="14" t="n"/>
-      <c r="G6" s="14" t="n"/>
-      <c r="H6" s="14" t="n"/>
-      <c r="I6" s="14" t="n"/>
-      <c r="J6" s="14" t="n"/>
-      <c r="K6" s="14" t="n"/>
-      <c r="L6" s="14" t="n"/>
-      <c r="M6" s="14" t="n"/>
-      <c r="N6" s="14" t="n"/>
-      <c r="O6" s="14" t="n"/>
+      <c r="C6" s="47" t="n"/>
+      <c r="D6" s="47" t="n"/>
+      <c r="E6" s="47" t="n"/>
+      <c r="F6" s="47" t="n"/>
+      <c r="G6" s="47" t="n"/>
+      <c r="H6" s="47" t="n"/>
+      <c r="I6" s="47" t="n"/>
+      <c r="J6" s="47" t="n"/>
+      <c r="K6" s="47" t="n"/>
+      <c r="L6" s="47" t="n"/>
+      <c r="M6" s="47" t="n"/>
+      <c r="N6" s="47" t="n"/>
+      <c r="O6" s="47" t="n"/>
     </row>
     <row r="7" ht="15" customHeight="1">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="48" t="inlineStr">
         <is>
           <t>▶  월 납입 보험료</t>
         </is>
       </c>
-      <c r="C7" s="16" t="n"/>
-      <c r="D7" s="16" t="n"/>
-      <c r="E7" s="16" t="n"/>
-      <c r="F7" s="16" t="n"/>
-      <c r="G7" s="16" t="n"/>
-      <c r="H7" s="16" t="n"/>
-      <c r="I7" s="16" t="n"/>
-      <c r="J7" s="16" t="n"/>
-      <c r="K7" s="16" t="n"/>
-      <c r="L7" s="16" t="n"/>
-      <c r="M7" s="16" t="n"/>
-      <c r="N7" s="16" t="n"/>
-      <c r="O7" s="16">
+      <c r="C7" s="49" t="n"/>
+      <c r="D7" s="49" t="n"/>
+      <c r="E7" s="49" t="n"/>
+      <c r="F7" s="49" t="n"/>
+      <c r="G7" s="49" t="n"/>
+      <c r="H7" s="49" t="n"/>
+      <c r="I7" s="49" t="n"/>
+      <c r="J7" s="49" t="n"/>
+      <c r="K7" s="49" t="n"/>
+      <c r="L7" s="49" t="n"/>
+      <c r="M7" s="49" t="n"/>
+      <c r="N7" s="49" t="n"/>
+      <c r="O7" s="49">
         <f>SUM(C7:N7)</f>
         <v/>
       </c>

--- a/templates/master_template_12.xlsx
+++ b/templates/master_template_12.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="14">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -112,8 +112,25 @@
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Malgun Gothic"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Malgun Gothic"/>
+      <b val="1"/>
+      <color rgb="001B2A4A"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Malgun Gothic"/>
+      <color rgb="001B2A4A"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="28">
+  <fills count="41">
     <fill>
       <patternFill/>
     </fill>
@@ -274,6 +291,84 @@
       <patternFill patternType="solid">
         <fgColor rgb="006B3FA0"/>
         <bgColor rgb="006B3FA0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E74C3C"/>
+        <bgColor rgb="00E74C3C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E67E22"/>
+        <bgColor rgb="00E67E22"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F1C40F"/>
+        <bgColor rgb="00F1C40F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0027AE60"/>
+        <bgColor rgb="0027AE60"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002980B9"/>
+        <bgColor rgb="002980B9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008E44AD"/>
+        <bgColor rgb="008E44AD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001ABC9C"/>
+        <bgColor rgb="001ABC9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D35400"/>
+        <bgColor rgb="00D35400"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002ECC71"/>
+        <bgColor rgb="002ECC71"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="003498DB"/>
+        <bgColor rgb="003498DB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="009B59B6"/>
+        <bgColor rgb="009B59B6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0016A085"/>
+        <bgColor rgb="0016A085"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F0F4FA"/>
+        <bgColor rgb="00F0F4FA"/>
       </patternFill>
     </fill>
   </fills>
@@ -407,7 +502,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -547,6 +642,45 @@
     </xf>
     <xf numFmtId="3" fontId="11" fillId="27" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="28" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="29" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="30" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="31" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="32" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="33" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="34" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="35" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="36" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="37" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="38" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="39" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="40" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -973,73 +1107,73 @@
     </row>
     <row r="3" ht="40" customHeight="1">
       <c r="A3" s="43" t="n"/>
-      <c r="C3" s="44" t="inlineStr">
+      <c r="C3" s="50" t="inlineStr">
         <is>
           <t>상품1
 (보험사)</t>
         </is>
       </c>
-      <c r="D3" s="44" t="inlineStr">
+      <c r="D3" s="51" t="inlineStr">
         <is>
           <t>상품2
 (보험사)</t>
         </is>
       </c>
-      <c r="E3" s="44" t="inlineStr">
+      <c r="E3" s="52" t="inlineStr">
         <is>
           <t>상품3
 (보험사)</t>
         </is>
       </c>
-      <c r="F3" s="44" t="inlineStr">
+      <c r="F3" s="53" t="inlineStr">
         <is>
           <t>상품4
 (보험사)</t>
         </is>
       </c>
-      <c r="G3" s="44" t="inlineStr">
+      <c r="G3" s="54" t="inlineStr">
         <is>
           <t>상품5
 (보험사)</t>
         </is>
       </c>
-      <c r="H3" s="44" t="inlineStr">
+      <c r="H3" s="55" t="inlineStr">
         <is>
           <t>상품6
 (보험사)</t>
         </is>
       </c>
-      <c r="I3" s="44" t="inlineStr">
+      <c r="I3" s="56" t="inlineStr">
         <is>
           <t>상품7
 (보험사)</t>
         </is>
       </c>
-      <c r="J3" s="44" t="inlineStr">
+      <c r="J3" s="57" t="inlineStr">
         <is>
           <t>상품8
 (보험사)</t>
         </is>
       </c>
-      <c r="K3" s="44" t="inlineStr">
+      <c r="K3" s="58" t="inlineStr">
         <is>
           <t>상품9
 (보험사)</t>
         </is>
       </c>
-      <c r="L3" s="44" t="inlineStr">
+      <c r="L3" s="59" t="inlineStr">
         <is>
           <t>상품10
 (보험사)</t>
         </is>
       </c>
-      <c r="M3" s="44" t="inlineStr">
+      <c r="M3" s="60" t="inlineStr">
         <is>
           <t>상품11
 (보험사)</t>
         </is>
       </c>
-      <c r="N3" s="44" t="inlineStr">
+      <c r="N3" s="61" t="inlineStr">
         <is>
           <t>상품12
 (보험사)</t>
@@ -1053,19 +1187,19 @@
           <t>가입년,월</t>
         </is>
       </c>
-      <c r="C4" s="47" t="n"/>
-      <c r="D4" s="47" t="n"/>
-      <c r="E4" s="47" t="n"/>
-      <c r="F4" s="47" t="n"/>
-      <c r="G4" s="47" t="n"/>
-      <c r="H4" s="47" t="n"/>
-      <c r="I4" s="47" t="n"/>
-      <c r="J4" s="47" t="n"/>
-      <c r="K4" s="47" t="n"/>
-      <c r="L4" s="47" t="n"/>
-      <c r="M4" s="47" t="n"/>
-      <c r="N4" s="47" t="n"/>
-      <c r="O4" s="47" t="n"/>
+      <c r="C4" s="62" t="n"/>
+      <c r="D4" s="62" t="n"/>
+      <c r="E4" s="62" t="n"/>
+      <c r="F4" s="62" t="n"/>
+      <c r="G4" s="62" t="n"/>
+      <c r="H4" s="62" t="n"/>
+      <c r="I4" s="62" t="n"/>
+      <c r="J4" s="62" t="n"/>
+      <c r="K4" s="62" t="n"/>
+      <c r="L4" s="62" t="n"/>
+      <c r="M4" s="62" t="n"/>
+      <c r="N4" s="62" t="n"/>
+      <c r="O4" s="62" t="n"/>
     </row>
     <row r="5" ht="12" customHeight="1">
       <c r="A5" s="46" t="inlineStr">
@@ -1073,19 +1207,19 @@
           <t>납입기간</t>
         </is>
       </c>
-      <c r="C5" s="47" t="n"/>
-      <c r="D5" s="47" t="n"/>
-      <c r="E5" s="47" t="n"/>
-      <c r="F5" s="47" t="n"/>
-      <c r="G5" s="47" t="n"/>
-      <c r="H5" s="47" t="n"/>
-      <c r="I5" s="47" t="n"/>
-      <c r="J5" s="47" t="n"/>
-      <c r="K5" s="47" t="n"/>
-      <c r="L5" s="47" t="n"/>
-      <c r="M5" s="47" t="n"/>
-      <c r="N5" s="47" t="n"/>
-      <c r="O5" s="47" t="n"/>
+      <c r="C5" s="62" t="n"/>
+      <c r="D5" s="62" t="n"/>
+      <c r="E5" s="62" t="n"/>
+      <c r="F5" s="62" t="n"/>
+      <c r="G5" s="62" t="n"/>
+      <c r="H5" s="62" t="n"/>
+      <c r="I5" s="62" t="n"/>
+      <c r="J5" s="62" t="n"/>
+      <c r="K5" s="62" t="n"/>
+      <c r="L5" s="62" t="n"/>
+      <c r="M5" s="62" t="n"/>
+      <c r="N5" s="62" t="n"/>
+      <c r="O5" s="62" t="n"/>
     </row>
     <row r="6" ht="12" customHeight="1">
       <c r="A6" s="46" t="inlineStr">
@@ -1093,19 +1227,19 @@
           <t>총납입개월</t>
         </is>
       </c>
-      <c r="C6" s="47" t="n"/>
-      <c r="D6" s="47" t="n"/>
-      <c r="E6" s="47" t="n"/>
-      <c r="F6" s="47" t="n"/>
-      <c r="G6" s="47" t="n"/>
-      <c r="H6" s="47" t="n"/>
-      <c r="I6" s="47" t="n"/>
-      <c r="J6" s="47" t="n"/>
-      <c r="K6" s="47" t="n"/>
-      <c r="L6" s="47" t="n"/>
-      <c r="M6" s="47" t="n"/>
-      <c r="N6" s="47" t="n"/>
-      <c r="O6" s="47" t="n"/>
+      <c r="C6" s="62" t="n"/>
+      <c r="D6" s="62" t="n"/>
+      <c r="E6" s="62" t="n"/>
+      <c r="F6" s="62" t="n"/>
+      <c r="G6" s="62" t="n"/>
+      <c r="H6" s="62" t="n"/>
+      <c r="I6" s="62" t="n"/>
+      <c r="J6" s="62" t="n"/>
+      <c r="K6" s="62" t="n"/>
+      <c r="L6" s="62" t="n"/>
+      <c r="M6" s="62" t="n"/>
+      <c r="N6" s="62" t="n"/>
+      <c r="O6" s="62" t="n"/>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" s="48" t="inlineStr">

--- a/templates/master_template_12.xlsx
+++ b/templates/master_template_12.xlsx
@@ -130,7 +130,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="41">
+  <fills count="53">
     <fill>
       <patternFill/>
     </fill>
@@ -369,6 +369,78 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F0F4FA"/>
         <bgColor rgb="00F0F4FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F1948A"/>
+        <bgColor rgb="00F1948A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F0B27A"/>
+        <bgColor rgb="00F0B27A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F9E79F"/>
+        <bgColor rgb="00F9E79F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0082E0AA"/>
+        <bgColor rgb="0082E0AA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0085C1E9"/>
+        <bgColor rgb="0085C1E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C39BD3"/>
+        <bgColor rgb="00C39BD3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0076D7C4"/>
+        <bgColor rgb="0076D7C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E59866"/>
+        <bgColor rgb="00E59866"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00ABEBC6"/>
+        <bgColor rgb="00ABEBC6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00AED6F1"/>
+        <bgColor rgb="00AED6F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D2B4DE"/>
+        <bgColor rgb="00D2B4DE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A3E4D7"/>
+        <bgColor rgb="00A3E4D7"/>
       </patternFill>
     </fill>
   </fills>
@@ -502,7 +574,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -680,6 +752,42 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="40" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="41" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="42" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="43" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="44" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="45" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="46" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="47" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="48" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="49" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="50" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="51" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="52" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1107,73 +1215,73 @@
     </row>
     <row r="3" ht="40" customHeight="1">
       <c r="A3" s="43" t="n"/>
-      <c r="C3" s="50" t="inlineStr">
+      <c r="C3" s="63" t="inlineStr">
         <is>
           <t>상품1
 (보험사)</t>
         </is>
       </c>
-      <c r="D3" s="51" t="inlineStr">
+      <c r="D3" s="64" t="inlineStr">
         <is>
           <t>상품2
 (보험사)</t>
         </is>
       </c>
-      <c r="E3" s="52" t="inlineStr">
+      <c r="E3" s="65" t="inlineStr">
         <is>
           <t>상품3
 (보험사)</t>
         </is>
       </c>
-      <c r="F3" s="53" t="inlineStr">
+      <c r="F3" s="66" t="inlineStr">
         <is>
           <t>상품4
 (보험사)</t>
         </is>
       </c>
-      <c r="G3" s="54" t="inlineStr">
+      <c r="G3" s="67" t="inlineStr">
         <is>
           <t>상품5
 (보험사)</t>
         </is>
       </c>
-      <c r="H3" s="55" t="inlineStr">
+      <c r="H3" s="68" t="inlineStr">
         <is>
           <t>상품6
 (보험사)</t>
         </is>
       </c>
-      <c r="I3" s="56" t="inlineStr">
+      <c r="I3" s="69" t="inlineStr">
         <is>
           <t>상품7
 (보험사)</t>
         </is>
       </c>
-      <c r="J3" s="57" t="inlineStr">
+      <c r="J3" s="70" t="inlineStr">
         <is>
           <t>상품8
 (보험사)</t>
         </is>
       </c>
-      <c r="K3" s="58" t="inlineStr">
+      <c r="K3" s="71" t="inlineStr">
         <is>
           <t>상품9
 (보험사)</t>
         </is>
       </c>
-      <c r="L3" s="59" t="inlineStr">
+      <c r="L3" s="72" t="inlineStr">
         <is>
           <t>상품10
 (보험사)</t>
         </is>
       </c>
-      <c r="M3" s="60" t="inlineStr">
+      <c r="M3" s="73" t="inlineStr">
         <is>
           <t>상품11
 (보험사)</t>
         </is>
       </c>
-      <c r="N3" s="61" t="inlineStr">
+      <c r="N3" s="74" t="inlineStr">
         <is>
           <t>상품12
 (보험사)</t>

--- a/templates/master_template_12.xlsx
+++ b/templates/master_template_12.xlsx
@@ -130,7 +130,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="53">
+  <fills count="65">
     <fill>
       <patternFill/>
     </fill>
@@ -441,6 +441,78 @@
       <patternFill patternType="solid">
         <fgColor rgb="00A3E4D7"/>
         <bgColor rgb="00A3E4D7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FDE8D0"/>
+        <bgColor rgb="00FDE8D0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FACDA6"/>
+        <bgColor rgb="00FACDA6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F7B27A"/>
+        <bgColor rgb="00F7B27A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4974E"/>
+        <bgColor rgb="00F4974E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F07D24"/>
+        <bgColor rgb="00F07D24"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D96A10"/>
+        <bgColor rgb="00D96A10"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF0E0"/>
+        <bgColor rgb="00FEF0E0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FBD9B3"/>
+        <bgColor rgb="00FBD9B3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8C48A"/>
+        <bgColor rgb="00F8C48A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5AE60"/>
+        <bgColor rgb="00F5AE60"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F29838"/>
+        <bgColor rgb="00F29838"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E0780A"/>
+        <bgColor rgb="00E0780A"/>
       </patternFill>
     </fill>
   </fills>
@@ -574,7 +646,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -788,6 +860,42 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="52" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="53" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="54" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="55" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="56" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="57" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="58" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="59" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="60" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="61" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="62" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="63" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="64" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1215,73 +1323,73 @@
     </row>
     <row r="3" ht="40" customHeight="1">
       <c r="A3" s="43" t="n"/>
-      <c r="C3" s="63" t="inlineStr">
+      <c r="C3" s="75" t="inlineStr">
         <is>
           <t>상품1
 (보험사)</t>
         </is>
       </c>
-      <c r="D3" s="64" t="inlineStr">
+      <c r="D3" s="76" t="inlineStr">
         <is>
           <t>상품2
 (보험사)</t>
         </is>
       </c>
-      <c r="E3" s="65" t="inlineStr">
+      <c r="E3" s="77" t="inlineStr">
         <is>
           <t>상품3
 (보험사)</t>
         </is>
       </c>
-      <c r="F3" s="66" t="inlineStr">
+      <c r="F3" s="78" t="inlineStr">
         <is>
           <t>상품4
 (보험사)</t>
         </is>
       </c>
-      <c r="G3" s="67" t="inlineStr">
+      <c r="G3" s="79" t="inlineStr">
         <is>
           <t>상품5
 (보험사)</t>
         </is>
       </c>
-      <c r="H3" s="68" t="inlineStr">
+      <c r="H3" s="80" t="inlineStr">
         <is>
           <t>상품6
 (보험사)</t>
         </is>
       </c>
-      <c r="I3" s="69" t="inlineStr">
+      <c r="I3" s="81" t="inlineStr">
         <is>
           <t>상품7
 (보험사)</t>
         </is>
       </c>
-      <c r="J3" s="70" t="inlineStr">
+      <c r="J3" s="82" t="inlineStr">
         <is>
           <t>상품8
 (보험사)</t>
         </is>
       </c>
-      <c r="K3" s="71" t="inlineStr">
+      <c r="K3" s="83" t="inlineStr">
         <is>
           <t>상품9
 (보험사)</t>
         </is>
       </c>
-      <c r="L3" s="72" t="inlineStr">
+      <c r="L3" s="84" t="inlineStr">
         <is>
           <t>상품10
 (보험사)</t>
         </is>
       </c>
-      <c r="M3" s="73" t="inlineStr">
+      <c r="M3" s="85" t="inlineStr">
         <is>
           <t>상품11
 (보험사)</t>
         </is>
       </c>
-      <c r="N3" s="74" t="inlineStr">
+      <c r="N3" s="86" t="inlineStr">
         <is>
           <t>상품12
 (보험사)</t>

--- a/templates/master_template_12.xlsx
+++ b/templates/master_template_12.xlsx
@@ -130,7 +130,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="65">
+  <fills count="77">
     <fill>
       <patternFill/>
     </fill>
@@ -513,6 +513,78 @@
       <patternFill patternType="solid">
         <fgColor rgb="00E0780A"/>
         <bgColor rgb="00E0780A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A8D5F2"/>
+        <bgColor rgb="00A8D5F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="005BA3D9"/>
+        <bgColor rgb="005BA3D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D0E8F7"/>
+        <bgColor rgb="00D0E8F7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="003A7BBF"/>
+        <bgColor rgb="003A7BBF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="007EC4EA"/>
+        <bgColor rgb="007EC4EA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002B6DAE"/>
+        <bgColor rgb="002B6DAE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00BFE0F5"/>
+        <bgColor rgb="00BFE0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004A94CC"/>
+        <bgColor rgb="004A94CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0090CBE8"/>
+        <bgColor rgb="0090CBE8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D8EDF9"/>
+        <bgColor rgb="00D8EDF9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="006BB0E0"/>
+        <bgColor rgb="006BB0E0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00336FA5"/>
+        <bgColor rgb="00336FA5"/>
       </patternFill>
     </fill>
   </fills>
@@ -646,7 +718,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="99">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -896,6 +968,42 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="64" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="65" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="66" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="67" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="68" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="69" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="70" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="71" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="72" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="73" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="74" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="75" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="76" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1323,73 +1431,73 @@
     </row>
     <row r="3" ht="40" customHeight="1">
       <c r="A3" s="43" t="n"/>
-      <c r="C3" s="75" t="inlineStr">
+      <c r="C3" s="87" t="inlineStr">
         <is>
           <t>상품1
 (보험사)</t>
         </is>
       </c>
-      <c r="D3" s="76" t="inlineStr">
+      <c r="D3" s="88" t="inlineStr">
         <is>
           <t>상품2
 (보험사)</t>
         </is>
       </c>
-      <c r="E3" s="77" t="inlineStr">
+      <c r="E3" s="89" t="inlineStr">
         <is>
           <t>상품3
 (보험사)</t>
         </is>
       </c>
-      <c r="F3" s="78" t="inlineStr">
+      <c r="F3" s="90" t="inlineStr">
         <is>
           <t>상품4
 (보험사)</t>
         </is>
       </c>
-      <c r="G3" s="79" t="inlineStr">
+      <c r="G3" s="91" t="inlineStr">
         <is>
           <t>상품5
 (보험사)</t>
         </is>
       </c>
-      <c r="H3" s="80" t="inlineStr">
+      <c r="H3" s="92" t="inlineStr">
         <is>
           <t>상품6
 (보험사)</t>
         </is>
       </c>
-      <c r="I3" s="81" t="inlineStr">
+      <c r="I3" s="93" t="inlineStr">
         <is>
           <t>상품7
 (보험사)</t>
         </is>
       </c>
-      <c r="J3" s="82" t="inlineStr">
+      <c r="J3" s="94" t="inlineStr">
         <is>
           <t>상품8
 (보험사)</t>
         </is>
       </c>
-      <c r="K3" s="83" t="inlineStr">
+      <c r="K3" s="95" t="inlineStr">
         <is>
           <t>상품9
 (보험사)</t>
         </is>
       </c>
-      <c r="L3" s="84" t="inlineStr">
+      <c r="L3" s="96" t="inlineStr">
         <is>
           <t>상품10
 (보험사)</t>
         </is>
       </c>
-      <c r="M3" s="85" t="inlineStr">
+      <c r="M3" s="97" t="inlineStr">
         <is>
           <t>상품11
 (보험사)</t>
         </is>
       </c>
-      <c r="N3" s="86" t="inlineStr">
+      <c r="N3" s="98" t="inlineStr">
         <is>
           <t>상품12
 (보험사)</t>

--- a/templates/master_template_12.xlsx
+++ b/templates/master_template_12.xlsx
@@ -130,7 +130,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="77">
+  <fills count="83">
     <fill>
       <patternFill/>
     </fill>
@@ -585,6 +585,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="00336FA5"/>
         <bgColor rgb="00336FA5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004180B8"/>
+        <bgColor rgb="004180B8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="005497C6"/>
+        <bgColor rgb="005497C6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002E72B2"/>
+        <bgColor rgb="002E72B2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="006AA5D4"/>
+        <bgColor rgb="006AA5D4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="003D82C1"/>
+        <bgColor rgb="003D82C1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004E90C0"/>
+        <bgColor rgb="004E90C0"/>
       </patternFill>
     </fill>
   </fills>
@@ -718,7 +754,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="99">
+  <cellXfs count="105">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1004,6 +1040,24 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="76" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="77" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="78" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="79" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="80" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="81" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="82" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1431,73 +1485,73 @@
     </row>
     <row r="3" ht="40" customHeight="1">
       <c r="A3" s="43" t="n"/>
-      <c r="C3" s="87" t="inlineStr">
+      <c r="C3" s="94" t="inlineStr">
         <is>
           <t>상품1
 (보험사)</t>
         </is>
       </c>
-      <c r="D3" s="88" t="inlineStr">
+      <c r="D3" s="92" t="inlineStr">
         <is>
           <t>상품2
 (보험사)</t>
         </is>
       </c>
-      <c r="E3" s="89" t="inlineStr">
+      <c r="E3" s="97" t="inlineStr">
         <is>
           <t>상품3
 (보험사)</t>
         </is>
       </c>
-      <c r="F3" s="90" t="inlineStr">
+      <c r="F3" s="98" t="inlineStr">
         <is>
           <t>상품4
 (보험사)</t>
         </is>
       </c>
-      <c r="G3" s="91" t="inlineStr">
+      <c r="G3" s="88" t="inlineStr">
         <is>
           <t>상품5
 (보험사)</t>
         </is>
       </c>
-      <c r="H3" s="92" t="inlineStr">
+      <c r="H3" s="90" t="inlineStr">
         <is>
           <t>상품6
 (보험사)</t>
         </is>
       </c>
-      <c r="I3" s="93" t="inlineStr">
+      <c r="I3" s="99" t="inlineStr">
         <is>
           <t>상품7
 (보험사)</t>
         </is>
       </c>
-      <c r="J3" s="94" t="inlineStr">
+      <c r="J3" s="100" t="inlineStr">
         <is>
           <t>상품8
 (보험사)</t>
         </is>
       </c>
-      <c r="K3" s="95" t="inlineStr">
+      <c r="K3" s="101" t="inlineStr">
         <is>
           <t>상품9
 (보험사)</t>
         </is>
       </c>
-      <c r="L3" s="96" t="inlineStr">
+      <c r="L3" s="102" t="inlineStr">
         <is>
           <t>상품10
 (보험사)</t>
         </is>
       </c>
-      <c r="M3" s="97" t="inlineStr">
+      <c r="M3" s="103" t="inlineStr">
         <is>
           <t>상품11
 (보험사)</t>
         </is>
       </c>
-      <c r="N3" s="98" t="inlineStr">
+      <c r="N3" s="104" t="inlineStr">
         <is>
           <t>상품12
 (보험사)</t>
